--- a/calculator/kalkulyator-kp-sellera.xlsx
+++ b/calculator/kalkulyator-kp-sellera.xlsx
@@ -12,7 +12,63 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="brand">Ввод!$B$5</definedName>
+    <definedName name="niche">Ввод!$B$6</definedName>
+    <definedName name="mp_rev">Ввод!$B$7</definedName>
+    <definedName name="mp_aov">Ввод!$B$8</definedName>
+    <definedName name="mp_take">Ввод!$B$9</definedName>
+    <definedName name="cogs">Ввод!$B$10</definedName>
+    <definedName name="wordstat">Ввод!$B$11</definedName>
+    <definedName name="followers">Ввод!$B$12</definedName>
+    <definedName name="freq">Ввод!$B$13</definedName>
+    <definedName name="stock">Ввод!$B$14</definedName>
+    <definedName name="acq">Ввод!$B$33</definedName>
+    <definedName name="ship">Ввод!$B$34</definedName>
+    <definedName name="pick">Ввод!$B$35</definedName>
+    <definedName name="crm_pct">Ввод!$B$36</definedName>
+    <definedName name="brand_cost">Ввод!$B$37</definedName>
+    <definedName name="platform">Ввод!$B$38</definedName>
+    <definedName name="svc_setup">Ввод!$B$41</definedName>
+    <definedName name="svc_month">Ввод!$B$42</definedName>
+    <definedName name="svc_pct">Ввод!$B$43</definedName>
+    <definedName name="conv_base_1">Ввод!$B$19</definedName>
+    <definedName name="conv_base_2">Ввод!$C$19</definedName>
+    <definedName name="conv_base_3">Ввод!$D$19</definedName>
+    <definedName name="base_site_1">Ввод!$B$20</definedName>
+    <definedName name="base_site_2">Ввод!$C$20</definedName>
+    <definedName name="base_site_3">Ввод!$D$20</definedName>
+    <definedName name="brand_share_1">Ввод!$B$21</definedName>
+    <definedName name="brand_share_2">Ввод!$C$21</definedName>
+    <definedName name="brand_share_3">Ввод!$D$21</definedName>
+    <definedName name="brand_cr_1">Ввод!$B$22</definedName>
+    <definedName name="brand_cr_2">Ввод!$C$22</definedName>
+    <definedName name="brand_cr_3">Ввод!$D$22</definedName>
+    <definedName name="social_cr_1">Ввод!$B$23</definedName>
+    <definedName name="social_cr_2">Ввод!$C$23</definedName>
+    <definedName name="social_cr_3">Ввод!$D$23</definedName>
+    <definedName name="ads_budget_1">Ввод!$B$24</definedName>
+    <definedName name="ads_budget_2">Ввод!$C$24</definedName>
+    <definedName name="ads_budget_3">Ввод!$D$24</definedName>
+    <definedName name="cpc_1">Ввод!$B$25</definedName>
+    <definedName name="cpc_2">Ввод!$C$25</definedName>
+    <definedName name="cpc_3">Ввод!$D$25</definedName>
+    <definedName name="ads_cr_1">Ввод!$B$26</definedName>
+    <definedName name="ads_cr_2">Ввод!$C$26</definedName>
+    <definedName name="ads_cr_3">Ввод!$D$26</definedName>
+    <definedName name="aov_k_1">Ввод!$B$27</definedName>
+    <definedName name="aov_k_2">Ввод!$C$27</definedName>
+    <definedName name="aov_k_3">Ввод!$D$27</definedName>
+    <definedName name="incr_1">Ввод!$B$28</definedName>
+    <definedName name="incr_2">Ввод!$C$28</definedName>
+    <definedName name="incr_3">Ввод!$D$28</definedName>
+    <definedName name="churn_1">Ввод!$B$29</definedName>
+    <definedName name="churn_2">Ввод!$C$29</definedName>
+    <definedName name="churn_3">Ввод!$D$29</definedName>
+    <definedName name="ramp_1">Ввод!$B$30</definedName>
+    <definedName name="ramp_2">Ввод!$C$30</definedName>
+    <definedName name="ramp_3">Ввод!$D$30</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -601,7 +657,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>Ввод!$B$7</f>
+        <f>mp_rev</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -614,7 +670,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>Ввод!$B$7*Ввод!$B$9</f>
+        <f>mp_rev*mp_take</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -627,7 +683,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>Ввод!$B$7*Ввод!$B$9*12</f>
+        <f>mp_rev*mp_take*12</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -640,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>Ввод!$B$14</f>
+        <f>stock</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -653,7 +709,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>Ввод!$B$11</f>
+        <f>wordstat</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -761,15 +817,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>Расчёт!Y17/Ввод!$B$7</f>
+        <f>Расчёт!Y17/mp_rev</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>Расчёт!Y42/Ввод!$B$7</f>
+        <f>Расчёт!Y42/mp_rev</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>Расчёт!Y67/Ввод!$B$7</f>
+        <f>Расчёт!Y67/mp_rev</f>
         <v/>
       </c>
     </row>
@@ -934,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1215,11 +1271,11 @@
         <v>0.03</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Вкладыш/QR на гарантию, инструкцию или бонус в Telegram-боте. Прямой призыв «купи на сайте» нарушает правила МП</t>
+          <t>QR на гарантию/инструкцию в Telegram-боте, адрес сайта в чате WB (разрешено). По рынку 1–5% заказов (не проверено). Нельзя: «бонус за отзыв» (штраф WB 50 000 ₽), контакты во вкладышах Ozon</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1292,7 @@
         <v>0.35</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1254,10 +1310,10 @@
         <v>0.1</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1275,10 +1331,10 @@
         <v>0.02</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1296,10 +1352,10 @@
         <v>0.002</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -1314,15 +1370,19 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="C24" s="21" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D24" s="21" t="n">
         <v>100000</v>
       </c>
-      <c r="D24" s="21" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Холодная реклама на старте обычно в минус, окупается позже</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1376,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1411,71 +1471,75 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Отток базы в месяц (перестают покупать)</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Без оттока база растёт бесконечно; 4–6% в месяц — около половины за год</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>Месяцев до выхода на полную мощность</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B30" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D30" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Разгон: SEO, база, оптимизация рекламы</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-    </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>3. Расходы своего сайта</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Эквайринг, % от выручки сайта</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>СБП 0,4–0,7%, карты около 2,8% (ЮKassa)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Доставка до ПВЗ, ₽/заказ (за счёт продавца)</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="n">
-        <v>250</v>
+          <t>Эквайринг, % от выручки сайта</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>0.02</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Яндекс от 99 ₽, Ozon от 123 ₽, СДЭК от 250 ₽</t>
+          <t>СБП 0,4–0,7%, карты около 2,8% (ЮKassa)</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1484,15 +1548,15 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Сборка и упаковка, ₽/заказ</t>
+          <t>Доставка до ПВЗ, ₽/заказ (за счёт продавца)</t>
         </is>
       </c>
       <c r="B34" s="21" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Фулфилмент 50–75 ₽</t>
+          <t>Яндекс от 99 ₽, Ozon от 123 ₽, СДЭК от 250 ₽</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
@@ -1501,15 +1565,15 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Бонусы и рассылки, % от выручки базы</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
-        <v>0.07000000000000001</v>
+          <t>Сборка и упаковка, ₽/заказ</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>70</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Бонусы за покупку на сайте + сервис рассылок</t>
+          <t>Фулфилмент 50–75 ₽</t>
         </is>
       </c>
       <c r="D35" s="2" t="n"/>
@@ -1518,15 +1582,15 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Брендовая реклама и SEO, % от выручки бренд-трафика</t>
+          <t>Бонусы и рассылки, % от выручки базы</t>
         </is>
       </c>
       <c r="B36" s="22" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Защита бренда в Директе</t>
+          <t>Бонусы за покупку на сайте + сервис рассылок</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
@@ -1535,63 +1599,67 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Платформа, CRM, сервисы, ₽/мес</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>15000</v>
+          <t>Брендовая реклама и SEO, % от выручки бренд-трафика</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n">
+        <v>0.05</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>InSales/Битрикс + CRM + бот</t>
+          <t>Защита бренда в Директе</t>
         </is>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Платформа, CRM, сервисы, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>InSales/Битрикс + CRM + бот</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>4. Наши услуги (для КП)</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Запуск под ключ, ₽ (разово)</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Сопровождение, ₽/мес</t>
+          <t>Запуск под ключ, ₽ (разово)</t>
         </is>
       </c>
       <c r="B41" s="21" t="n">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Трафик, CRM, аналитика</t>
+          <t>Подставь свою цену</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
@@ -1600,19 +1668,36 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Процент с продаж сайта</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="n">
-        <v>0</v>
+          <t>Сопровождение, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="n">
+        <v>50000</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Если работаешь за результат</t>
+          <t>Подставь свою цену</t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Процент с продаж сайта</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Если работаешь за результат</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1861,99 +1946,99 @@
         </is>
       </c>
       <c r="B6" s="30">
-        <f>MIN(1,B5/Ввод!$B$29)</f>
+        <f>MIN(1,B5/ramp_1)</f>
         <v/>
       </c>
       <c r="C6" s="30">
-        <f>MIN(1,C5/Ввод!$B$29)</f>
+        <f>MIN(1,C5/ramp_1)</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>MIN(1,D5/Ввод!$B$29)</f>
+        <f>MIN(1,D5/ramp_1)</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>MIN(1,E5/Ввод!$B$29)</f>
+        <f>MIN(1,E5/ramp_1)</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>MIN(1,F5/Ввод!$B$29)</f>
+        <f>MIN(1,F5/ramp_1)</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>MIN(1,G5/Ввод!$B$29)</f>
+        <f>MIN(1,G5/ramp_1)</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>MIN(1,H5/Ввод!$B$29)</f>
+        <f>MIN(1,H5/ramp_1)</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>MIN(1,I5/Ввод!$B$29)</f>
+        <f>MIN(1,I5/ramp_1)</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>MIN(1,J5/Ввод!$B$29)</f>
+        <f>MIN(1,J5/ramp_1)</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>MIN(1,K5/Ввод!$B$29)</f>
+        <f>MIN(1,K5/ramp_1)</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>MIN(1,L5/Ввод!$B$29)</f>
+        <f>MIN(1,L5/ramp_1)</f>
         <v/>
       </c>
       <c r="M6" s="30">
-        <f>MIN(1,M5/Ввод!$B$29)</f>
+        <f>MIN(1,M5/ramp_1)</f>
         <v/>
       </c>
       <c r="N6" s="30">
-        <f>MIN(1,N5/Ввод!$B$29)</f>
+        <f>MIN(1,N5/ramp_1)</f>
         <v/>
       </c>
       <c r="O6" s="30">
-        <f>MIN(1,O5/Ввод!$B$29)</f>
+        <f>MIN(1,O5/ramp_1)</f>
         <v/>
       </c>
       <c r="P6" s="30">
-        <f>MIN(1,P5/Ввод!$B$29)</f>
+        <f>MIN(1,P5/ramp_1)</f>
         <v/>
       </c>
       <c r="Q6" s="30">
-        <f>MIN(1,Q5/Ввод!$B$29)</f>
+        <f>MIN(1,Q5/ramp_1)</f>
         <v/>
       </c>
       <c r="R6" s="30">
-        <f>MIN(1,R5/Ввод!$B$29)</f>
+        <f>MIN(1,R5/ramp_1)</f>
         <v/>
       </c>
       <c r="S6" s="30">
-        <f>MIN(1,S5/Ввод!$B$29)</f>
+        <f>MIN(1,S5/ramp_1)</f>
         <v/>
       </c>
       <c r="T6" s="30">
-        <f>MIN(1,T5/Ввод!$B$29)</f>
+        <f>MIN(1,T5/ramp_1)</f>
         <v/>
       </c>
       <c r="U6" s="30">
-        <f>MIN(1,U5/Ввод!$B$29)</f>
+        <f>MIN(1,U5/ramp_1)</f>
         <v/>
       </c>
       <c r="V6" s="30">
-        <f>MIN(1,V5/Ввод!$B$29)</f>
+        <f>MIN(1,V5/ramp_1)</f>
         <v/>
       </c>
       <c r="W6" s="30">
-        <f>MIN(1,W5/Ввод!$B$29)</f>
+        <f>MIN(1,W5/ramp_1)</f>
         <v/>
       </c>
       <c r="X6" s="30">
-        <f>MIN(1,X5/Ввод!$B$29)</f>
+        <f>MIN(1,X5/ramp_1)</f>
         <v/>
       </c>
       <c r="Y6" s="30">
-        <f>MIN(1,Y5/Ввод!$B$29)</f>
+        <f>MIN(1,Y5/ramp_1)</f>
         <v/>
       </c>
     </row>
@@ -1964,202 +2049,202 @@
         </is>
       </c>
       <c r="B7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="C7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="D7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="E7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="F7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="G7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="H7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="I7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="J7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="K7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="L7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="M7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="N7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="O7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="P7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Q7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="R7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="S7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="T7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="U7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="V7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="W7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="X7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Y7" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Новых людей в базе</t>
+          <t>Новых людей в базе (с МП + новые покупатели сайта)</t>
         </is>
       </c>
       <c r="B8" s="31">
-        <f>B7*Ввод!$B$19*B6</f>
+        <f>B7*conv_base_1*B6+B11+B12+B13</f>
         <v/>
       </c>
       <c r="C8" s="31">
-        <f>C7*Ввод!$B$19*C6</f>
+        <f>C7*conv_base_1*C6+C11+C12+C13</f>
         <v/>
       </c>
       <c r="D8" s="31">
-        <f>D7*Ввод!$B$19*D6</f>
+        <f>D7*conv_base_1*D6+D11+D12+D13</f>
         <v/>
       </c>
       <c r="E8" s="31">
-        <f>E7*Ввод!$B$19*E6</f>
+        <f>E7*conv_base_1*E6+E11+E12+E13</f>
         <v/>
       </c>
       <c r="F8" s="31">
-        <f>F7*Ввод!$B$19*F6</f>
+        <f>F7*conv_base_1*F6+F11+F12+F13</f>
         <v/>
       </c>
       <c r="G8" s="31">
-        <f>G7*Ввод!$B$19*G6</f>
+        <f>G7*conv_base_1*G6+G11+G12+G13</f>
         <v/>
       </c>
       <c r="H8" s="31">
-        <f>H7*Ввод!$B$19*H6</f>
+        <f>H7*conv_base_1*H6+H11+H12+H13</f>
         <v/>
       </c>
       <c r="I8" s="31">
-        <f>I7*Ввод!$B$19*I6</f>
+        <f>I7*conv_base_1*I6+I11+I12+I13</f>
         <v/>
       </c>
       <c r="J8" s="31">
-        <f>J7*Ввод!$B$19*J6</f>
+        <f>J7*conv_base_1*J6+J11+J12+J13</f>
         <v/>
       </c>
       <c r="K8" s="31">
-        <f>K7*Ввод!$B$19*K6</f>
+        <f>K7*conv_base_1*K6+K11+K12+K13</f>
         <v/>
       </c>
       <c r="L8" s="31">
-        <f>L7*Ввод!$B$19*L6</f>
+        <f>L7*conv_base_1*L6+L11+L12+L13</f>
         <v/>
       </c>
       <c r="M8" s="31">
-        <f>M7*Ввод!$B$19*M6</f>
+        <f>M7*conv_base_1*M6+M11+M12+M13</f>
         <v/>
       </c>
       <c r="N8" s="31">
-        <f>N7*Ввод!$B$19*N6</f>
+        <f>N7*conv_base_1*N6+N11+N12+N13</f>
         <v/>
       </c>
       <c r="O8" s="31">
-        <f>O7*Ввод!$B$19*O6</f>
+        <f>O7*conv_base_1*O6+O11+O12+O13</f>
         <v/>
       </c>
       <c r="P8" s="31">
-        <f>P7*Ввод!$B$19*P6</f>
+        <f>P7*conv_base_1*P6+P11+P12+P13</f>
         <v/>
       </c>
       <c r="Q8" s="31">
-        <f>Q7*Ввод!$B$19*Q6</f>
+        <f>Q7*conv_base_1*Q6+Q11+Q12+Q13</f>
         <v/>
       </c>
       <c r="R8" s="31">
-        <f>R7*Ввод!$B$19*R6</f>
+        <f>R7*conv_base_1*R6+R11+R12+R13</f>
         <v/>
       </c>
       <c r="S8" s="31">
-        <f>S7*Ввод!$B$19*S6</f>
+        <f>S7*conv_base_1*S6+S11+S12+S13</f>
         <v/>
       </c>
       <c r="T8" s="31">
-        <f>T7*Ввод!$B$19*T6</f>
+        <f>T7*conv_base_1*T6+T11+T12+T13</f>
         <v/>
       </c>
       <c r="U8" s="31">
-        <f>U7*Ввод!$B$19*U6</f>
+        <f>U7*conv_base_1*U6+U11+U12+U13</f>
         <v/>
       </c>
       <c r="V8" s="31">
-        <f>V7*Ввод!$B$19*V6</f>
+        <f>V7*conv_base_1*V6+V11+V12+V13</f>
         <v/>
       </c>
       <c r="W8" s="31">
-        <f>W7*Ввод!$B$19*W6</f>
+        <f>W7*conv_base_1*W6+W11+W12+W13</f>
         <v/>
       </c>
       <c r="X8" s="31">
-        <f>X7*Ввод!$B$19*X6</f>
+        <f>X7*conv_base_1*X6+X11+X12+X13</f>
         <v/>
       </c>
       <c r="Y8" s="31">
-        <f>Y7*Ввод!$B$19*Y6</f>
+        <f>Y7*conv_base_1*Y6+Y11+Y12+Y13</f>
         <v/>
       </c>
     </row>
@@ -2174,95 +2259,95 @@
         <v/>
       </c>
       <c r="C9" s="31">
-        <f>B9+C8</f>
+        <f>B9*(1-churn_1)+C8</f>
         <v/>
       </c>
       <c r="D9" s="31">
-        <f>C9+D8</f>
+        <f>C9*(1-churn_1)+D8</f>
         <v/>
       </c>
       <c r="E9" s="31">
-        <f>D9+E8</f>
+        <f>D9*(1-churn_1)+E8</f>
         <v/>
       </c>
       <c r="F9" s="31">
-        <f>E9+F8</f>
+        <f>E9*(1-churn_1)+F8</f>
         <v/>
       </c>
       <c r="G9" s="31">
-        <f>F9+G8</f>
+        <f>F9*(1-churn_1)+G8</f>
         <v/>
       </c>
       <c r="H9" s="31">
-        <f>G9+H8</f>
+        <f>G9*(1-churn_1)+H8</f>
         <v/>
       </c>
       <c r="I9" s="31">
-        <f>H9+I8</f>
+        <f>H9*(1-churn_1)+I8</f>
         <v/>
       </c>
       <c r="J9" s="31">
-        <f>I9+J8</f>
+        <f>I9*(1-churn_1)+J8</f>
         <v/>
       </c>
       <c r="K9" s="31">
-        <f>J9+K8</f>
+        <f>J9*(1-churn_1)+K8</f>
         <v/>
       </c>
       <c r="L9" s="31">
-        <f>K9+L8</f>
+        <f>K9*(1-churn_1)+L8</f>
         <v/>
       </c>
       <c r="M9" s="31">
-        <f>L9+M8</f>
+        <f>L9*(1-churn_1)+M8</f>
         <v/>
       </c>
       <c r="N9" s="31">
-        <f>M9+N8</f>
+        <f>M9*(1-churn_1)+N8</f>
         <v/>
       </c>
       <c r="O9" s="31">
-        <f>N9+O8</f>
+        <f>N9*(1-churn_1)+O8</f>
         <v/>
       </c>
       <c r="P9" s="31">
-        <f>O9+P8</f>
+        <f>O9*(1-churn_1)+P8</f>
         <v/>
       </c>
       <c r="Q9" s="31">
-        <f>P9+Q8</f>
+        <f>P9*(1-churn_1)+Q8</f>
         <v/>
       </c>
       <c r="R9" s="31">
-        <f>Q9+R8</f>
+        <f>Q9*(1-churn_1)+R8</f>
         <v/>
       </c>
       <c r="S9" s="31">
-        <f>R9+S8</f>
+        <f>R9*(1-churn_1)+S8</f>
         <v/>
       </c>
       <c r="T9" s="31">
-        <f>S9+T8</f>
+        <f>S9*(1-churn_1)+T8</f>
         <v/>
       </c>
       <c r="U9" s="31">
-        <f>T9+U8</f>
+        <f>T9*(1-churn_1)+U8</f>
         <v/>
       </c>
       <c r="V9" s="31">
-        <f>U9+V8</f>
+        <f>U9*(1-churn_1)+V8</f>
         <v/>
       </c>
       <c r="W9" s="31">
-        <f>V9+W8</f>
+        <f>V9*(1-churn_1)+W8</f>
         <v/>
       </c>
       <c r="X9" s="31">
-        <f>W9+X8</f>
+        <f>W9*(1-churn_1)+X8</f>
         <v/>
       </c>
       <c r="Y9" s="31">
-        <f>X9+Y8</f>
+        <f>X9*(1-churn_1)+Y8</f>
         <v/>
       </c>
     </row>
@@ -2273,99 +2358,99 @@
         </is>
       </c>
       <c r="B10" s="32">
-        <f>0*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>0*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>B9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>B9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="D10" s="32">
-        <f>C9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>C9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>D9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>D9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="F10" s="32">
-        <f>E9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>E9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="G10" s="32">
-        <f>F9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>F9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="H10" s="32">
-        <f>G9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>G9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="I10" s="32">
-        <f>H9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>H9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="J10" s="32">
-        <f>I9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>I9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="K10" s="32">
-        <f>J9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>J9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="L10" s="32">
-        <f>K9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>K9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="M10" s="32">
-        <f>L9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>L9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="N10" s="32">
-        <f>M9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>M9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="O10" s="32">
-        <f>N9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>N9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="P10" s="32">
-        <f>O9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>O9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="Q10" s="32">
-        <f>P9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>P9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="R10" s="32">
-        <f>Q9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>Q9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="S10" s="32">
-        <f>R9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>R9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="T10" s="32">
-        <f>S9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>S9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="U10" s="32">
-        <f>T9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>T9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="V10" s="32">
-        <f>U9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>U9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="W10" s="32">
-        <f>V9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>V9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="X10" s="32">
-        <f>W9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>W9*freq/12*base_site_1</f>
         <v/>
       </c>
       <c r="Y10" s="32">
-        <f>X9*Ввод!$B$13/12*Ввод!$B$20</f>
+        <f>X9*freq/12*base_site_1</f>
         <v/>
       </c>
     </row>
@@ -2376,99 +2461,99 @@
         </is>
       </c>
       <c r="B11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*B6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*B6*brand_cr_1</f>
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*C6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*C6*brand_cr_1</f>
         <v/>
       </c>
       <c r="D11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*D6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*D6*brand_cr_1</f>
         <v/>
       </c>
       <c r="E11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*E6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*E6*brand_cr_1</f>
         <v/>
       </c>
       <c r="F11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*F6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*F6*brand_cr_1</f>
         <v/>
       </c>
       <c r="G11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*G6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*G6*brand_cr_1</f>
         <v/>
       </c>
       <c r="H11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*H6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*H6*brand_cr_1</f>
         <v/>
       </c>
       <c r="I11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*I6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*I6*brand_cr_1</f>
         <v/>
       </c>
       <c r="J11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*J6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*J6*brand_cr_1</f>
         <v/>
       </c>
       <c r="K11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*K6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*K6*brand_cr_1</f>
         <v/>
       </c>
       <c r="L11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*L6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*L6*brand_cr_1</f>
         <v/>
       </c>
       <c r="M11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*M6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*M6*brand_cr_1</f>
         <v/>
       </c>
       <c r="N11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*N6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*N6*brand_cr_1</f>
         <v/>
       </c>
       <c r="O11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*O6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*O6*brand_cr_1</f>
         <v/>
       </c>
       <c r="P11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*P6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*P6*brand_cr_1</f>
         <v/>
       </c>
       <c r="Q11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*Q6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*Q6*brand_cr_1</f>
         <v/>
       </c>
       <c r="R11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*R6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*R6*brand_cr_1</f>
         <v/>
       </c>
       <c r="S11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*S6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*S6*brand_cr_1</f>
         <v/>
       </c>
       <c r="T11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*T6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*T6*brand_cr_1</f>
         <v/>
       </c>
       <c r="U11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*U6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*U6*brand_cr_1</f>
         <v/>
       </c>
       <c r="V11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*V6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*V6*brand_cr_1</f>
         <v/>
       </c>
       <c r="W11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*W6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*W6*brand_cr_1</f>
         <v/>
       </c>
       <c r="X11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*X6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*X6*brand_cr_1</f>
         <v/>
       </c>
       <c r="Y11" s="32">
-        <f>Ввод!$B$11*Ввод!$B$21*Y6*Ввод!$B$22</f>
+        <f>wordstat*brand_share_1*Y6*brand_cr_1</f>
         <v/>
       </c>
     </row>
@@ -2479,99 +2564,99 @@
         </is>
       </c>
       <c r="B12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*B6</f>
+        <f>followers*social_cr_1*B6</f>
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*C6</f>
+        <f>followers*social_cr_1*C6</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*D6</f>
+        <f>followers*social_cr_1*D6</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*E6</f>
+        <f>followers*social_cr_1*E6</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*F6</f>
+        <f>followers*social_cr_1*F6</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*G6</f>
+        <f>followers*social_cr_1*G6</f>
         <v/>
       </c>
       <c r="H12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*H6</f>
+        <f>followers*social_cr_1*H6</f>
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*I6</f>
+        <f>followers*social_cr_1*I6</f>
         <v/>
       </c>
       <c r="J12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*J6</f>
+        <f>followers*social_cr_1*J6</f>
         <v/>
       </c>
       <c r="K12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*K6</f>
+        <f>followers*social_cr_1*K6</f>
         <v/>
       </c>
       <c r="L12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*L6</f>
+        <f>followers*social_cr_1*L6</f>
         <v/>
       </c>
       <c r="M12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*M6</f>
+        <f>followers*social_cr_1*M6</f>
         <v/>
       </c>
       <c r="N12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*N6</f>
+        <f>followers*social_cr_1*N6</f>
         <v/>
       </c>
       <c r="O12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*O6</f>
+        <f>followers*social_cr_1*O6</f>
         <v/>
       </c>
       <c r="P12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*P6</f>
+        <f>followers*social_cr_1*P6</f>
         <v/>
       </c>
       <c r="Q12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*Q6</f>
+        <f>followers*social_cr_1*Q6</f>
         <v/>
       </c>
       <c r="R12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*R6</f>
+        <f>followers*social_cr_1*R6</f>
         <v/>
       </c>
       <c r="S12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*S6</f>
+        <f>followers*social_cr_1*S6</f>
         <v/>
       </c>
       <c r="T12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*T6</f>
+        <f>followers*social_cr_1*T6</f>
         <v/>
       </c>
       <c r="U12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*U6</f>
+        <f>followers*social_cr_1*U6</f>
         <v/>
       </c>
       <c r="V12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*V6</f>
+        <f>followers*social_cr_1*V6</f>
         <v/>
       </c>
       <c r="W12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*W6</f>
+        <f>followers*social_cr_1*W6</f>
         <v/>
       </c>
       <c r="X12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*X6</f>
+        <f>followers*social_cr_1*X6</f>
         <v/>
       </c>
       <c r="Y12" s="32">
-        <f>Ввод!$B$12*Ввод!$B$23*Y6</f>
+        <f>followers*social_cr_1*Y6</f>
         <v/>
       </c>
     </row>
@@ -2582,99 +2667,99 @@
         </is>
       </c>
       <c r="B13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*B6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*B6)</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*C6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*C6)</f>
         <v/>
       </c>
       <c r="D13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*D6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*D6)</f>
         <v/>
       </c>
       <c r="E13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*E6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*E6)</f>
         <v/>
       </c>
       <c r="F13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*F6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*F6)</f>
         <v/>
       </c>
       <c r="G13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*G6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*G6)</f>
         <v/>
       </c>
       <c r="H13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*H6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*H6)</f>
         <v/>
       </c>
       <c r="I13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*I6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*I6)</f>
         <v/>
       </c>
       <c r="J13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*J6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*J6)</f>
         <v/>
       </c>
       <c r="K13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*K6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*K6)</f>
         <v/>
       </c>
       <c r="L13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*L6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*L6)</f>
         <v/>
       </c>
       <c r="M13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*M6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*M6)</f>
         <v/>
       </c>
       <c r="N13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*N6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*N6)</f>
         <v/>
       </c>
       <c r="O13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*O6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*O6)</f>
         <v/>
       </c>
       <c r="P13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*P6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*P6)</f>
         <v/>
       </c>
       <c r="Q13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*Q6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*Q6)</f>
         <v/>
       </c>
       <c r="R13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*R6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*R6)</f>
         <v/>
       </c>
       <c r="S13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*S6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*S6)</f>
         <v/>
       </c>
       <c r="T13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*T6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*T6)</f>
         <v/>
       </c>
       <c r="U13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*U6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*U6)</f>
         <v/>
       </c>
       <c r="V13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*V6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*V6)</f>
         <v/>
       </c>
       <c r="W13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*W6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*W6)</f>
         <v/>
       </c>
       <c r="X13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*X6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*X6)</f>
         <v/>
       </c>
       <c r="Y13" s="32">
-        <f>Ввод!$B$24/Ввод!$B$25*Ввод!$B$26*(0.5+0.5*Y6)</f>
+        <f>ads_budget_1/cpc_1*ads_cr_1*(0.5+0.5*Y6)</f>
         <v/>
       </c>
     </row>
@@ -2788,99 +2873,99 @@
         </is>
       </c>
       <c r="B15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="C15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="D15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="F15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="G15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="H15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="I15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="J15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="K15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="L15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="M15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="N15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="O15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="P15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="Q15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="R15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="S15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="T15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="U15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="V15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="W15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="X15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
       <c r="Y15" s="33">
-        <f>Ввод!$B$8*Ввод!$B$27</f>
+        <f>mp_aov*aov_k_1</f>
         <v/>
       </c>
     </row>
@@ -2994,99 +3079,99 @@
         </is>
       </c>
       <c r="B17" s="33">
-        <f>B16*Ввод!$B$28</f>
+        <f>B16*incr_1</f>
         <v/>
       </c>
       <c r="C17" s="33">
-        <f>C16*Ввод!$B$28</f>
+        <f>C16*incr_1</f>
         <v/>
       </c>
       <c r="D17" s="33">
-        <f>D16*Ввод!$B$28</f>
+        <f>D16*incr_1</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>E16*Ввод!$B$28</f>
+        <f>E16*incr_1</f>
         <v/>
       </c>
       <c r="F17" s="33">
-        <f>F16*Ввод!$B$28</f>
+        <f>F16*incr_1</f>
         <v/>
       </c>
       <c r="G17" s="33">
-        <f>G16*Ввод!$B$28</f>
+        <f>G16*incr_1</f>
         <v/>
       </c>
       <c r="H17" s="33">
-        <f>H16*Ввод!$B$28</f>
+        <f>H16*incr_1</f>
         <v/>
       </c>
       <c r="I17" s="33">
-        <f>I16*Ввод!$B$28</f>
+        <f>I16*incr_1</f>
         <v/>
       </c>
       <c r="J17" s="33">
-        <f>J16*Ввод!$B$28</f>
+        <f>J16*incr_1</f>
         <v/>
       </c>
       <c r="K17" s="33">
-        <f>K16*Ввод!$B$28</f>
+        <f>K16*incr_1</f>
         <v/>
       </c>
       <c r="L17" s="33">
-        <f>L16*Ввод!$B$28</f>
+        <f>L16*incr_1</f>
         <v/>
       </c>
       <c r="M17" s="33">
-        <f>M16*Ввод!$B$28</f>
+        <f>M16*incr_1</f>
         <v/>
       </c>
       <c r="N17" s="33">
-        <f>N16*Ввод!$B$28</f>
+        <f>N16*incr_1</f>
         <v/>
       </c>
       <c r="O17" s="33">
-        <f>O16*Ввод!$B$28</f>
+        <f>O16*incr_1</f>
         <v/>
       </c>
       <c r="P17" s="33">
-        <f>P16*Ввод!$B$28</f>
+        <f>P16*incr_1</f>
         <v/>
       </c>
       <c r="Q17" s="33">
-        <f>Q16*Ввод!$B$28</f>
+        <f>Q16*incr_1</f>
         <v/>
       </c>
       <c r="R17" s="33">
-        <f>R16*Ввод!$B$28</f>
+        <f>R16*incr_1</f>
         <v/>
       </c>
       <c r="S17" s="33">
-        <f>S16*Ввод!$B$28</f>
+        <f>S16*incr_1</f>
         <v/>
       </c>
       <c r="T17" s="33">
-        <f>T16*Ввод!$B$28</f>
+        <f>T16*incr_1</f>
         <v/>
       </c>
       <c r="U17" s="33">
-        <f>U16*Ввод!$B$28</f>
+        <f>U16*incr_1</f>
         <v/>
       </c>
       <c r="V17" s="33">
-        <f>V16*Ввод!$B$28</f>
+        <f>V16*incr_1</f>
         <v/>
       </c>
       <c r="W17" s="33">
-        <f>W16*Ввод!$B$28</f>
+        <f>W16*incr_1</f>
         <v/>
       </c>
       <c r="X17" s="33">
-        <f>X16*Ввод!$B$28</f>
+        <f>X16*incr_1</f>
         <v/>
       </c>
       <c r="Y17" s="33">
-        <f>Y16*Ввод!$B$28</f>
+        <f>Y16*incr_1</f>
         <v/>
       </c>
     </row>
@@ -3200,99 +3285,99 @@
         </is>
       </c>
       <c r="B19" s="35">
-        <f>B16/(Ввод!$B$7-B18+B16)</f>
+        <f>B16/(mp_rev-B18+B16)</f>
         <v/>
       </c>
       <c r="C19" s="35">
-        <f>C16/(Ввод!$B$7-C18+C16)</f>
+        <f>C16/(mp_rev-C18+C16)</f>
         <v/>
       </c>
       <c r="D19" s="35">
-        <f>D16/(Ввод!$B$7-D18+D16)</f>
+        <f>D16/(mp_rev-D18+D16)</f>
         <v/>
       </c>
       <c r="E19" s="35">
-        <f>E16/(Ввод!$B$7-E18+E16)</f>
+        <f>E16/(mp_rev-E18+E16)</f>
         <v/>
       </c>
       <c r="F19" s="35">
-        <f>F16/(Ввод!$B$7-F18+F16)</f>
+        <f>F16/(mp_rev-F18+F16)</f>
         <v/>
       </c>
       <c r="G19" s="35">
-        <f>G16/(Ввод!$B$7-G18+G16)</f>
+        <f>G16/(mp_rev-G18+G16)</f>
         <v/>
       </c>
       <c r="H19" s="35">
-        <f>H16/(Ввод!$B$7-H18+H16)</f>
+        <f>H16/(mp_rev-H18+H16)</f>
         <v/>
       </c>
       <c r="I19" s="35">
-        <f>I16/(Ввод!$B$7-I18+I16)</f>
+        <f>I16/(mp_rev-I18+I16)</f>
         <v/>
       </c>
       <c r="J19" s="35">
-        <f>J16/(Ввод!$B$7-J18+J16)</f>
+        <f>J16/(mp_rev-J18+J16)</f>
         <v/>
       </c>
       <c r="K19" s="35">
-        <f>K16/(Ввод!$B$7-K18+K16)</f>
+        <f>K16/(mp_rev-K18+K16)</f>
         <v/>
       </c>
       <c r="L19" s="35">
-        <f>L16/(Ввод!$B$7-L18+L16)</f>
+        <f>L16/(mp_rev-L18+L16)</f>
         <v/>
       </c>
       <c r="M19" s="35">
-        <f>M16/(Ввод!$B$7-M18+M16)</f>
+        <f>M16/(mp_rev-M18+M16)</f>
         <v/>
       </c>
       <c r="N19" s="35">
-        <f>N16/(Ввод!$B$7-N18+N16)</f>
+        <f>N16/(mp_rev-N18+N16)</f>
         <v/>
       </c>
       <c r="O19" s="35">
-        <f>O16/(Ввод!$B$7-O18+O16)</f>
+        <f>O16/(mp_rev-O18+O16)</f>
         <v/>
       </c>
       <c r="P19" s="35">
-        <f>P16/(Ввод!$B$7-P18+P16)</f>
+        <f>P16/(mp_rev-P18+P16)</f>
         <v/>
       </c>
       <c r="Q19" s="35">
-        <f>Q16/(Ввод!$B$7-Q18+Q16)</f>
+        <f>Q16/(mp_rev-Q18+Q16)</f>
         <v/>
       </c>
       <c r="R19" s="35">
-        <f>R16/(Ввод!$B$7-R18+R16)</f>
+        <f>R16/(mp_rev-R18+R16)</f>
         <v/>
       </c>
       <c r="S19" s="35">
-        <f>S16/(Ввод!$B$7-S18+S16)</f>
+        <f>S16/(mp_rev-S18+S16)</f>
         <v/>
       </c>
       <c r="T19" s="35">
-        <f>T16/(Ввод!$B$7-T18+T16)</f>
+        <f>T16/(mp_rev-T18+T16)</f>
         <v/>
       </c>
       <c r="U19" s="35">
-        <f>U16/(Ввод!$B$7-U18+U16)</f>
+        <f>U16/(mp_rev-U18+U16)</f>
         <v/>
       </c>
       <c r="V19" s="35">
-        <f>V16/(Ввод!$B$7-V18+V16)</f>
+        <f>V16/(mp_rev-V18+V16)</f>
         <v/>
       </c>
       <c r="W19" s="35">
-        <f>W16/(Ввод!$B$7-W18+W16)</f>
+        <f>W16/(mp_rev-W18+W16)</f>
         <v/>
       </c>
       <c r="X19" s="35">
-        <f>X16/(Ввод!$B$7-X18+X16)</f>
+        <f>X16/(mp_rev-X18+X16)</f>
         <v/>
       </c>
       <c r="Y19" s="35">
-        <f>Y16/(Ввод!$B$7-Y18+Y16)</f>
+        <f>Y16/(mp_rev-Y18+Y16)</f>
         <v/>
       </c>
     </row>
@@ -3303,99 +3388,99 @@
         </is>
       </c>
       <c r="B20" s="33">
-        <f>B16*Ввод!$B$32+B14*(Ввод!$B$33+Ввод!$B$34)+B10*B15*Ввод!$B$35+B11*B15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>B16*acq+B14*(ship+pick)+B10*B15*crm_pct+B11*B15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="C20" s="33">
-        <f>C16*Ввод!$B$32+C14*(Ввод!$B$33+Ввод!$B$34)+C10*C15*Ввод!$B$35+C11*C15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>C16*acq+C14*(ship+pick)+C10*C15*crm_pct+C11*C15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="D20" s="33">
-        <f>D16*Ввод!$B$32+D14*(Ввод!$B$33+Ввод!$B$34)+D10*D15*Ввод!$B$35+D11*D15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>D16*acq+D14*(ship+pick)+D10*D15*crm_pct+D11*D15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="E20" s="33">
-        <f>E16*Ввод!$B$32+E14*(Ввод!$B$33+Ввод!$B$34)+E10*E15*Ввод!$B$35+E11*E15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>E16*acq+E14*(ship+pick)+E10*E15*crm_pct+E11*E15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="F20" s="33">
-        <f>F16*Ввод!$B$32+F14*(Ввод!$B$33+Ввод!$B$34)+F10*F15*Ввод!$B$35+F11*F15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>F16*acq+F14*(ship+pick)+F10*F15*crm_pct+F11*F15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="G20" s="33">
-        <f>G16*Ввод!$B$32+G14*(Ввод!$B$33+Ввод!$B$34)+G10*G15*Ввод!$B$35+G11*G15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>G16*acq+G14*(ship+pick)+G10*G15*crm_pct+G11*G15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="H20" s="33">
-        <f>H16*Ввод!$B$32+H14*(Ввод!$B$33+Ввод!$B$34)+H10*H15*Ввод!$B$35+H11*H15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>H16*acq+H14*(ship+pick)+H10*H15*crm_pct+H11*H15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="I20" s="33">
-        <f>I16*Ввод!$B$32+I14*(Ввод!$B$33+Ввод!$B$34)+I10*I15*Ввод!$B$35+I11*I15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>I16*acq+I14*(ship+pick)+I10*I15*crm_pct+I11*I15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="J20" s="33">
-        <f>J16*Ввод!$B$32+J14*(Ввод!$B$33+Ввод!$B$34)+J10*J15*Ввод!$B$35+J11*J15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>J16*acq+J14*(ship+pick)+J10*J15*crm_pct+J11*J15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="K20" s="33">
-        <f>K16*Ввод!$B$32+K14*(Ввод!$B$33+Ввод!$B$34)+K10*K15*Ввод!$B$35+K11*K15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>K16*acq+K14*(ship+pick)+K10*K15*crm_pct+K11*K15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="L20" s="33">
-        <f>L16*Ввод!$B$32+L14*(Ввод!$B$33+Ввод!$B$34)+L10*L15*Ввод!$B$35+L11*L15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>L16*acq+L14*(ship+pick)+L10*L15*crm_pct+L11*L15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="M20" s="33">
-        <f>M16*Ввод!$B$32+M14*(Ввод!$B$33+Ввод!$B$34)+M10*M15*Ввод!$B$35+M11*M15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>M16*acq+M14*(ship+pick)+M10*M15*crm_pct+M11*M15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="N20" s="33">
-        <f>N16*Ввод!$B$32+N14*(Ввод!$B$33+Ввод!$B$34)+N10*N15*Ввод!$B$35+N11*N15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>N16*acq+N14*(ship+pick)+N10*N15*crm_pct+N11*N15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="O20" s="33">
-        <f>O16*Ввод!$B$32+O14*(Ввод!$B$33+Ввод!$B$34)+O10*O15*Ввод!$B$35+O11*O15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>O16*acq+O14*(ship+pick)+O10*O15*crm_pct+O11*O15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="P20" s="33">
-        <f>P16*Ввод!$B$32+P14*(Ввод!$B$33+Ввод!$B$34)+P10*P15*Ввод!$B$35+P11*P15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>P16*acq+P14*(ship+pick)+P10*P15*crm_pct+P11*P15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="Q20" s="33">
-        <f>Q16*Ввод!$B$32+Q14*(Ввод!$B$33+Ввод!$B$34)+Q10*Q15*Ввод!$B$35+Q11*Q15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>Q16*acq+Q14*(ship+pick)+Q10*Q15*crm_pct+Q11*Q15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="R20" s="33">
-        <f>R16*Ввод!$B$32+R14*(Ввод!$B$33+Ввод!$B$34)+R10*R15*Ввод!$B$35+R11*R15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>R16*acq+R14*(ship+pick)+R10*R15*crm_pct+R11*R15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="S20" s="33">
-        <f>S16*Ввод!$B$32+S14*(Ввод!$B$33+Ввод!$B$34)+S10*S15*Ввод!$B$35+S11*S15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>S16*acq+S14*(ship+pick)+S10*S15*crm_pct+S11*S15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="T20" s="33">
-        <f>T16*Ввод!$B$32+T14*(Ввод!$B$33+Ввод!$B$34)+T10*T15*Ввод!$B$35+T11*T15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>T16*acq+T14*(ship+pick)+T10*T15*crm_pct+T11*T15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="U20" s="33">
-        <f>U16*Ввод!$B$32+U14*(Ввод!$B$33+Ввод!$B$34)+U10*U15*Ввод!$B$35+U11*U15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>U16*acq+U14*(ship+pick)+U10*U15*crm_pct+U11*U15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="V20" s="33">
-        <f>V16*Ввод!$B$32+V14*(Ввод!$B$33+Ввод!$B$34)+V10*V15*Ввод!$B$35+V11*V15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>V16*acq+V14*(ship+pick)+V10*V15*crm_pct+V11*V15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="W20" s="33">
-        <f>W16*Ввод!$B$32+W14*(Ввод!$B$33+Ввод!$B$34)+W10*W15*Ввод!$B$35+W11*W15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>W16*acq+W14*(ship+pick)+W10*W15*crm_pct+W11*W15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="X20" s="33">
-        <f>X16*Ввод!$B$32+X14*(Ввод!$B$33+Ввод!$B$34)+X10*X15*Ввод!$B$35+X11*X15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>X16*acq+X14*(ship+pick)+X10*X15*crm_pct+X11*X15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
       <c r="Y20" s="33">
-        <f>Y16*Ввод!$B$32+Y14*(Ввод!$B$33+Ввод!$B$34)+Y10*Y15*Ввод!$B$35+Y11*Y15*Ввод!$B$36+Ввод!$B$24+Ввод!$B$37</f>
+        <f>Y16*acq+Y14*(ship+pick)+Y10*Y15*crm_pct+Y11*Y15*brand_cost+ads_budget_1+platform</f>
         <v/>
       </c>
     </row>
@@ -3509,99 +3594,99 @@
         </is>
       </c>
       <c r="B22" s="33">
-        <f>Ввод!$B$40+Ввод!$B$41+B16*Ввод!$B$42</f>
+        <f>svc_setup+svc_month+B16*svc_pct</f>
         <v/>
       </c>
       <c r="C22" s="33">
-        <f>Ввод!$B$41+C16*Ввод!$B$42</f>
+        <f>svc_month+C16*svc_pct</f>
         <v/>
       </c>
       <c r="D22" s="33">
-        <f>Ввод!$B$41+D16*Ввод!$B$42</f>
+        <f>svc_month+D16*svc_pct</f>
         <v/>
       </c>
       <c r="E22" s="33">
-        <f>Ввод!$B$41+E16*Ввод!$B$42</f>
+        <f>svc_month+E16*svc_pct</f>
         <v/>
       </c>
       <c r="F22" s="33">
-        <f>Ввод!$B$41+F16*Ввод!$B$42</f>
+        <f>svc_month+F16*svc_pct</f>
         <v/>
       </c>
       <c r="G22" s="33">
-        <f>Ввод!$B$41+G16*Ввод!$B$42</f>
+        <f>svc_month+G16*svc_pct</f>
         <v/>
       </c>
       <c r="H22" s="33">
-        <f>Ввод!$B$41+H16*Ввод!$B$42</f>
+        <f>svc_month+H16*svc_pct</f>
         <v/>
       </c>
       <c r="I22" s="33">
-        <f>Ввод!$B$41+I16*Ввод!$B$42</f>
+        <f>svc_month+I16*svc_pct</f>
         <v/>
       </c>
       <c r="J22" s="33">
-        <f>Ввод!$B$41+J16*Ввод!$B$42</f>
+        <f>svc_month+J16*svc_pct</f>
         <v/>
       </c>
       <c r="K22" s="33">
-        <f>Ввод!$B$41+K16*Ввод!$B$42</f>
+        <f>svc_month+K16*svc_pct</f>
         <v/>
       </c>
       <c r="L22" s="33">
-        <f>Ввод!$B$41+L16*Ввод!$B$42</f>
+        <f>svc_month+L16*svc_pct</f>
         <v/>
       </c>
       <c r="M22" s="33">
-        <f>Ввод!$B$41+M16*Ввод!$B$42</f>
+        <f>svc_month+M16*svc_pct</f>
         <v/>
       </c>
       <c r="N22" s="33">
-        <f>Ввод!$B$41+N16*Ввод!$B$42</f>
+        <f>svc_month+N16*svc_pct</f>
         <v/>
       </c>
       <c r="O22" s="33">
-        <f>Ввод!$B$41+O16*Ввод!$B$42</f>
+        <f>svc_month+O16*svc_pct</f>
         <v/>
       </c>
       <c r="P22" s="33">
-        <f>Ввод!$B$41+P16*Ввод!$B$42</f>
+        <f>svc_month+P16*svc_pct</f>
         <v/>
       </c>
       <c r="Q22" s="33">
-        <f>Ввод!$B$41+Q16*Ввод!$B$42</f>
+        <f>svc_month+Q16*svc_pct</f>
         <v/>
       </c>
       <c r="R22" s="33">
-        <f>Ввод!$B$41+R16*Ввод!$B$42</f>
+        <f>svc_month+R16*svc_pct</f>
         <v/>
       </c>
       <c r="S22" s="33">
-        <f>Ввод!$B$41+S16*Ввод!$B$42</f>
+        <f>svc_month+S16*svc_pct</f>
         <v/>
       </c>
       <c r="T22" s="33">
-        <f>Ввод!$B$41+T16*Ввод!$B$42</f>
+        <f>svc_month+T16*svc_pct</f>
         <v/>
       </c>
       <c r="U22" s="33">
-        <f>Ввод!$B$41+U16*Ввод!$B$42</f>
+        <f>svc_month+U16*svc_pct</f>
         <v/>
       </c>
       <c r="V22" s="33">
-        <f>Ввод!$B$41+V16*Ввод!$B$42</f>
+        <f>svc_month+V16*svc_pct</f>
         <v/>
       </c>
       <c r="W22" s="33">
-        <f>Ввод!$B$41+W16*Ввод!$B$42</f>
+        <f>svc_month+W16*svc_pct</f>
         <v/>
       </c>
       <c r="X22" s="33">
-        <f>Ввод!$B$41+X16*Ввод!$B$42</f>
+        <f>svc_month+X16*svc_pct</f>
         <v/>
       </c>
       <c r="Y22" s="33">
-        <f>Ввод!$B$41+Y16*Ввод!$B$42</f>
+        <f>svc_month+Y16*svc_pct</f>
         <v/>
       </c>
     </row>
@@ -3612,99 +3697,99 @@
         </is>
       </c>
       <c r="B23" s="33">
-        <f>B16*(1-Ввод!$B$10)-B20-B22</f>
+        <f>B16*(1-cogs)-B20-B22</f>
         <v/>
       </c>
       <c r="C23" s="33">
-        <f>C16*(1-Ввод!$B$10)-C20-C22</f>
+        <f>C16*(1-cogs)-C20-C22</f>
         <v/>
       </c>
       <c r="D23" s="33">
-        <f>D16*(1-Ввод!$B$10)-D20-D22</f>
+        <f>D16*(1-cogs)-D20-D22</f>
         <v/>
       </c>
       <c r="E23" s="33">
-        <f>E16*(1-Ввод!$B$10)-E20-E22</f>
+        <f>E16*(1-cogs)-E20-E22</f>
         <v/>
       </c>
       <c r="F23" s="33">
-        <f>F16*(1-Ввод!$B$10)-F20-F22</f>
+        <f>F16*(1-cogs)-F20-F22</f>
         <v/>
       </c>
       <c r="G23" s="33">
-        <f>G16*(1-Ввод!$B$10)-G20-G22</f>
+        <f>G16*(1-cogs)-G20-G22</f>
         <v/>
       </c>
       <c r="H23" s="33">
-        <f>H16*(1-Ввод!$B$10)-H20-H22</f>
+        <f>H16*(1-cogs)-H20-H22</f>
         <v/>
       </c>
       <c r="I23" s="33">
-        <f>I16*(1-Ввод!$B$10)-I20-I22</f>
+        <f>I16*(1-cogs)-I20-I22</f>
         <v/>
       </c>
       <c r="J23" s="33">
-        <f>J16*(1-Ввод!$B$10)-J20-J22</f>
+        <f>J16*(1-cogs)-J20-J22</f>
         <v/>
       </c>
       <c r="K23" s="33">
-        <f>K16*(1-Ввод!$B$10)-K20-K22</f>
+        <f>K16*(1-cogs)-K20-K22</f>
         <v/>
       </c>
       <c r="L23" s="33">
-        <f>L16*(1-Ввод!$B$10)-L20-L22</f>
+        <f>L16*(1-cogs)-L20-L22</f>
         <v/>
       </c>
       <c r="M23" s="33">
-        <f>M16*(1-Ввод!$B$10)-M20-M22</f>
+        <f>M16*(1-cogs)-M20-M22</f>
         <v/>
       </c>
       <c r="N23" s="33">
-        <f>N16*(1-Ввод!$B$10)-N20-N22</f>
+        <f>N16*(1-cogs)-N20-N22</f>
         <v/>
       </c>
       <c r="O23" s="33">
-        <f>O16*(1-Ввод!$B$10)-O20-O22</f>
+        <f>O16*(1-cogs)-O20-O22</f>
         <v/>
       </c>
       <c r="P23" s="33">
-        <f>P16*(1-Ввод!$B$10)-P20-P22</f>
+        <f>P16*(1-cogs)-P20-P22</f>
         <v/>
       </c>
       <c r="Q23" s="33">
-        <f>Q16*(1-Ввод!$B$10)-Q20-Q22</f>
+        <f>Q16*(1-cogs)-Q20-Q22</f>
         <v/>
       </c>
       <c r="R23" s="33">
-        <f>R16*(1-Ввод!$B$10)-R20-R22</f>
+        <f>R16*(1-cogs)-R20-R22</f>
         <v/>
       </c>
       <c r="S23" s="33">
-        <f>S16*(1-Ввод!$B$10)-S20-S22</f>
+        <f>S16*(1-cogs)-S20-S22</f>
         <v/>
       </c>
       <c r="T23" s="33">
-        <f>T16*(1-Ввод!$B$10)-T20-T22</f>
+        <f>T16*(1-cogs)-T20-T22</f>
         <v/>
       </c>
       <c r="U23" s="33">
-        <f>U16*(1-Ввод!$B$10)-U20-U22</f>
+        <f>U16*(1-cogs)-U20-U22</f>
         <v/>
       </c>
       <c r="V23" s="33">
-        <f>V16*(1-Ввод!$B$10)-V20-V22</f>
+        <f>V16*(1-cogs)-V20-V22</f>
         <v/>
       </c>
       <c r="W23" s="33">
-        <f>W16*(1-Ввод!$B$10)-W20-W22</f>
+        <f>W16*(1-cogs)-W20-W22</f>
         <v/>
       </c>
       <c r="X23" s="33">
-        <f>X16*(1-Ввод!$B$10)-X20-X22</f>
+        <f>X16*(1-cogs)-X20-X22</f>
         <v/>
       </c>
       <c r="Y23" s="33">
-        <f>Y16*(1-Ввод!$B$10)-Y20-Y22</f>
+        <f>Y16*(1-cogs)-Y20-Y22</f>
         <v/>
       </c>
     </row>
@@ -3715,99 +3800,99 @@
         </is>
       </c>
       <c r="B24" s="33">
-        <f>B18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>B18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="C24" s="33">
-        <f>C18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>C18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="D24" s="33">
-        <f>D18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>D18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="E24" s="33">
-        <f>E18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>E18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="F24" s="33">
-        <f>F18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>F18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="G24" s="33">
-        <f>G18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>G18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="H24" s="33">
-        <f>H18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>H18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="I24" s="33">
-        <f>I18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>I18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="J24" s="33">
-        <f>J18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>J18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="K24" s="33">
-        <f>K18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>K18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="L24" s="33">
-        <f>L18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>L18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="M24" s="33">
-        <f>M18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>M18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="N24" s="33">
-        <f>N18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>N18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="O24" s="33">
-        <f>O18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>O18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="P24" s="33">
-        <f>P18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>P18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Q24" s="33">
-        <f>Q18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Q18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="R24" s="33">
-        <f>R18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>R18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="S24" s="33">
-        <f>S18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>S18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="T24" s="33">
-        <f>T18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>T18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="U24" s="33">
-        <f>U18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>U18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="V24" s="33">
-        <f>V18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>V18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="W24" s="33">
-        <f>W18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>W18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="X24" s="33">
-        <f>X18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>X18*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Y24" s="33">
-        <f>Y18*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Y18*(1-cogs-mp_take)</f>
         <v/>
       </c>
     </row>
@@ -4264,99 +4349,99 @@
         </is>
       </c>
       <c r="B31" s="30">
-        <f>MIN(1,B30/Ввод!$C$29)</f>
+        <f>MIN(1,B30/ramp_2)</f>
         <v/>
       </c>
       <c r="C31" s="30">
-        <f>MIN(1,C30/Ввод!$C$29)</f>
+        <f>MIN(1,C30/ramp_2)</f>
         <v/>
       </c>
       <c r="D31" s="30">
-        <f>MIN(1,D30/Ввод!$C$29)</f>
+        <f>MIN(1,D30/ramp_2)</f>
         <v/>
       </c>
       <c r="E31" s="30">
-        <f>MIN(1,E30/Ввод!$C$29)</f>
+        <f>MIN(1,E30/ramp_2)</f>
         <v/>
       </c>
       <c r="F31" s="30">
-        <f>MIN(1,F30/Ввод!$C$29)</f>
+        <f>MIN(1,F30/ramp_2)</f>
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>MIN(1,G30/Ввод!$C$29)</f>
+        <f>MIN(1,G30/ramp_2)</f>
         <v/>
       </c>
       <c r="H31" s="30">
-        <f>MIN(1,H30/Ввод!$C$29)</f>
+        <f>MIN(1,H30/ramp_2)</f>
         <v/>
       </c>
       <c r="I31" s="30">
-        <f>MIN(1,I30/Ввод!$C$29)</f>
+        <f>MIN(1,I30/ramp_2)</f>
         <v/>
       </c>
       <c r="J31" s="30">
-        <f>MIN(1,J30/Ввод!$C$29)</f>
+        <f>MIN(1,J30/ramp_2)</f>
         <v/>
       </c>
       <c r="K31" s="30">
-        <f>MIN(1,K30/Ввод!$C$29)</f>
+        <f>MIN(1,K30/ramp_2)</f>
         <v/>
       </c>
       <c r="L31" s="30">
-        <f>MIN(1,L30/Ввод!$C$29)</f>
+        <f>MIN(1,L30/ramp_2)</f>
         <v/>
       </c>
       <c r="M31" s="30">
-        <f>MIN(1,M30/Ввод!$C$29)</f>
+        <f>MIN(1,M30/ramp_2)</f>
         <v/>
       </c>
       <c r="N31" s="30">
-        <f>MIN(1,N30/Ввод!$C$29)</f>
+        <f>MIN(1,N30/ramp_2)</f>
         <v/>
       </c>
       <c r="O31" s="30">
-        <f>MIN(1,O30/Ввод!$C$29)</f>
+        <f>MIN(1,O30/ramp_2)</f>
         <v/>
       </c>
       <c r="P31" s="30">
-        <f>MIN(1,P30/Ввод!$C$29)</f>
+        <f>MIN(1,P30/ramp_2)</f>
         <v/>
       </c>
       <c r="Q31" s="30">
-        <f>MIN(1,Q30/Ввод!$C$29)</f>
+        <f>MIN(1,Q30/ramp_2)</f>
         <v/>
       </c>
       <c r="R31" s="30">
-        <f>MIN(1,R30/Ввод!$C$29)</f>
+        <f>MIN(1,R30/ramp_2)</f>
         <v/>
       </c>
       <c r="S31" s="30">
-        <f>MIN(1,S30/Ввод!$C$29)</f>
+        <f>MIN(1,S30/ramp_2)</f>
         <v/>
       </c>
       <c r="T31" s="30">
-        <f>MIN(1,T30/Ввод!$C$29)</f>
+        <f>MIN(1,T30/ramp_2)</f>
         <v/>
       </c>
       <c r="U31" s="30">
-        <f>MIN(1,U30/Ввод!$C$29)</f>
+        <f>MIN(1,U30/ramp_2)</f>
         <v/>
       </c>
       <c r="V31" s="30">
-        <f>MIN(1,V30/Ввод!$C$29)</f>
+        <f>MIN(1,V30/ramp_2)</f>
         <v/>
       </c>
       <c r="W31" s="30">
-        <f>MIN(1,W30/Ввод!$C$29)</f>
+        <f>MIN(1,W30/ramp_2)</f>
         <v/>
       </c>
       <c r="X31" s="30">
-        <f>MIN(1,X30/Ввод!$C$29)</f>
+        <f>MIN(1,X30/ramp_2)</f>
         <v/>
       </c>
       <c r="Y31" s="30">
-        <f>MIN(1,Y30/Ввод!$C$29)</f>
+        <f>MIN(1,Y30/ramp_2)</f>
         <v/>
       </c>
     </row>
@@ -4367,202 +4452,202 @@
         </is>
       </c>
       <c r="B32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="C32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="D32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="E32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="F32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="G32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="H32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="I32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="J32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="K32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="L32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="M32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="N32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="O32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="P32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Q32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="R32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="S32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="T32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="U32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="V32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="W32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="X32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Y32" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Новых людей в базе</t>
+          <t>Новых людей в базе (с МП + новые покупатели сайта)</t>
         </is>
       </c>
       <c r="B33" s="31">
-        <f>B32*Ввод!$C$19*B31</f>
+        <f>B32*conv_base_2*B31+B36+B37+B38</f>
         <v/>
       </c>
       <c r="C33" s="31">
-        <f>C32*Ввод!$C$19*C31</f>
+        <f>C32*conv_base_2*C31+C36+C37+C38</f>
         <v/>
       </c>
       <c r="D33" s="31">
-        <f>D32*Ввод!$C$19*D31</f>
+        <f>D32*conv_base_2*D31+D36+D37+D38</f>
         <v/>
       </c>
       <c r="E33" s="31">
-        <f>E32*Ввод!$C$19*E31</f>
+        <f>E32*conv_base_2*E31+E36+E37+E38</f>
         <v/>
       </c>
       <c r="F33" s="31">
-        <f>F32*Ввод!$C$19*F31</f>
+        <f>F32*conv_base_2*F31+F36+F37+F38</f>
         <v/>
       </c>
       <c r="G33" s="31">
-        <f>G32*Ввод!$C$19*G31</f>
+        <f>G32*conv_base_2*G31+G36+G37+G38</f>
         <v/>
       </c>
       <c r="H33" s="31">
-        <f>H32*Ввод!$C$19*H31</f>
+        <f>H32*conv_base_2*H31+H36+H37+H38</f>
         <v/>
       </c>
       <c r="I33" s="31">
-        <f>I32*Ввод!$C$19*I31</f>
+        <f>I32*conv_base_2*I31+I36+I37+I38</f>
         <v/>
       </c>
       <c r="J33" s="31">
-        <f>J32*Ввод!$C$19*J31</f>
+        <f>J32*conv_base_2*J31+J36+J37+J38</f>
         <v/>
       </c>
       <c r="K33" s="31">
-        <f>K32*Ввод!$C$19*K31</f>
+        <f>K32*conv_base_2*K31+K36+K37+K38</f>
         <v/>
       </c>
       <c r="L33" s="31">
-        <f>L32*Ввод!$C$19*L31</f>
+        <f>L32*conv_base_2*L31+L36+L37+L38</f>
         <v/>
       </c>
       <c r="M33" s="31">
-        <f>M32*Ввод!$C$19*M31</f>
+        <f>M32*conv_base_2*M31+M36+M37+M38</f>
         <v/>
       </c>
       <c r="N33" s="31">
-        <f>N32*Ввод!$C$19*N31</f>
+        <f>N32*conv_base_2*N31+N36+N37+N38</f>
         <v/>
       </c>
       <c r="O33" s="31">
-        <f>O32*Ввод!$C$19*O31</f>
+        <f>O32*conv_base_2*O31+O36+O37+O38</f>
         <v/>
       </c>
       <c r="P33" s="31">
-        <f>P32*Ввод!$C$19*P31</f>
+        <f>P32*conv_base_2*P31+P36+P37+P38</f>
         <v/>
       </c>
       <c r="Q33" s="31">
-        <f>Q32*Ввод!$C$19*Q31</f>
+        <f>Q32*conv_base_2*Q31+Q36+Q37+Q38</f>
         <v/>
       </c>
       <c r="R33" s="31">
-        <f>R32*Ввод!$C$19*R31</f>
+        <f>R32*conv_base_2*R31+R36+R37+R38</f>
         <v/>
       </c>
       <c r="S33" s="31">
-        <f>S32*Ввод!$C$19*S31</f>
+        <f>S32*conv_base_2*S31+S36+S37+S38</f>
         <v/>
       </c>
       <c r="T33" s="31">
-        <f>T32*Ввод!$C$19*T31</f>
+        <f>T32*conv_base_2*T31+T36+T37+T38</f>
         <v/>
       </c>
       <c r="U33" s="31">
-        <f>U32*Ввод!$C$19*U31</f>
+        <f>U32*conv_base_2*U31+U36+U37+U38</f>
         <v/>
       </c>
       <c r="V33" s="31">
-        <f>V32*Ввод!$C$19*V31</f>
+        <f>V32*conv_base_2*V31+V36+V37+V38</f>
         <v/>
       </c>
       <c r="W33" s="31">
-        <f>W32*Ввод!$C$19*W31</f>
+        <f>W32*conv_base_2*W31+W36+W37+W38</f>
         <v/>
       </c>
       <c r="X33" s="31">
-        <f>X32*Ввод!$C$19*X31</f>
+        <f>X32*conv_base_2*X31+X36+X37+X38</f>
         <v/>
       </c>
       <c r="Y33" s="31">
-        <f>Y32*Ввод!$C$19*Y31</f>
+        <f>Y32*conv_base_2*Y31+Y36+Y37+Y38</f>
         <v/>
       </c>
     </row>
@@ -4577,95 +4662,95 @@
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>B34+C33</f>
+        <f>B34*(1-churn_2)+C33</f>
         <v/>
       </c>
       <c r="D34" s="31">
-        <f>C34+D33</f>
+        <f>C34*(1-churn_2)+D33</f>
         <v/>
       </c>
       <c r="E34" s="31">
-        <f>D34+E33</f>
+        <f>D34*(1-churn_2)+E33</f>
         <v/>
       </c>
       <c r="F34" s="31">
-        <f>E34+F33</f>
+        <f>E34*(1-churn_2)+F33</f>
         <v/>
       </c>
       <c r="G34" s="31">
-        <f>F34+G33</f>
+        <f>F34*(1-churn_2)+G33</f>
         <v/>
       </c>
       <c r="H34" s="31">
-        <f>G34+H33</f>
+        <f>G34*(1-churn_2)+H33</f>
         <v/>
       </c>
       <c r="I34" s="31">
-        <f>H34+I33</f>
+        <f>H34*(1-churn_2)+I33</f>
         <v/>
       </c>
       <c r="J34" s="31">
-        <f>I34+J33</f>
+        <f>I34*(1-churn_2)+J33</f>
         <v/>
       </c>
       <c r="K34" s="31">
-        <f>J34+K33</f>
+        <f>J34*(1-churn_2)+K33</f>
         <v/>
       </c>
       <c r="L34" s="31">
-        <f>K34+L33</f>
+        <f>K34*(1-churn_2)+L33</f>
         <v/>
       </c>
       <c r="M34" s="31">
-        <f>L34+M33</f>
+        <f>L34*(1-churn_2)+M33</f>
         <v/>
       </c>
       <c r="N34" s="31">
-        <f>M34+N33</f>
+        <f>M34*(1-churn_2)+N33</f>
         <v/>
       </c>
       <c r="O34" s="31">
-        <f>N34+O33</f>
+        <f>N34*(1-churn_2)+O33</f>
         <v/>
       </c>
       <c r="P34" s="31">
-        <f>O34+P33</f>
+        <f>O34*(1-churn_2)+P33</f>
         <v/>
       </c>
       <c r="Q34" s="31">
-        <f>P34+Q33</f>
+        <f>P34*(1-churn_2)+Q33</f>
         <v/>
       </c>
       <c r="R34" s="31">
-        <f>Q34+R33</f>
+        <f>Q34*(1-churn_2)+R33</f>
         <v/>
       </c>
       <c r="S34" s="31">
-        <f>R34+S33</f>
+        <f>R34*(1-churn_2)+S33</f>
         <v/>
       </c>
       <c r="T34" s="31">
-        <f>S34+T33</f>
+        <f>S34*(1-churn_2)+T33</f>
         <v/>
       </c>
       <c r="U34" s="31">
-        <f>T34+U33</f>
+        <f>T34*(1-churn_2)+U33</f>
         <v/>
       </c>
       <c r="V34" s="31">
-        <f>U34+V33</f>
+        <f>U34*(1-churn_2)+V33</f>
         <v/>
       </c>
       <c r="W34" s="31">
-        <f>V34+W33</f>
+        <f>V34*(1-churn_2)+W33</f>
         <v/>
       </c>
       <c r="X34" s="31">
-        <f>W34+X33</f>
+        <f>W34*(1-churn_2)+X33</f>
         <v/>
       </c>
       <c r="Y34" s="31">
-        <f>X34+Y33</f>
+        <f>X34*(1-churn_2)+Y33</f>
         <v/>
       </c>
     </row>
@@ -4676,99 +4761,99 @@
         </is>
       </c>
       <c r="B35" s="32">
-        <f>0*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>0*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>B34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>B34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="D35" s="32">
-        <f>C34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>C34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>D34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>D34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>E34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>E34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="G35" s="32">
-        <f>F34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>F34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="H35" s="32">
-        <f>G34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>G34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="I35" s="32">
-        <f>H34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>H34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="J35" s="32">
-        <f>I34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>I34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="K35" s="32">
-        <f>J34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>J34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="L35" s="32">
-        <f>K34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>K34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="M35" s="32">
-        <f>L34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>L34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="N35" s="32">
-        <f>M34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>M34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="O35" s="32">
-        <f>N34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>N34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="P35" s="32">
-        <f>O34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>O34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="Q35" s="32">
-        <f>P34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>P34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="R35" s="32">
-        <f>Q34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>Q34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="S35" s="32">
-        <f>R34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>R34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="T35" s="32">
-        <f>S34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>S34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="U35" s="32">
-        <f>T34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>T34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="V35" s="32">
-        <f>U34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>U34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="W35" s="32">
-        <f>V34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>V34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="X35" s="32">
-        <f>W34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>W34*freq/12*base_site_2</f>
         <v/>
       </c>
       <c r="Y35" s="32">
-        <f>X34*Ввод!$B$13/12*Ввод!$C$20</f>
+        <f>X34*freq/12*base_site_2</f>
         <v/>
       </c>
     </row>
@@ -4779,99 +4864,99 @@
         </is>
       </c>
       <c r="B36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*B31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*B31*brand_cr_2</f>
         <v/>
       </c>
       <c r="C36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*C31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*C31*brand_cr_2</f>
         <v/>
       </c>
       <c r="D36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*D31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*D31*brand_cr_2</f>
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*E31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*E31*brand_cr_2</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*F31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*F31*brand_cr_2</f>
         <v/>
       </c>
       <c r="G36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*G31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*G31*brand_cr_2</f>
         <v/>
       </c>
       <c r="H36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*H31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*H31*brand_cr_2</f>
         <v/>
       </c>
       <c r="I36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*I31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*I31*brand_cr_2</f>
         <v/>
       </c>
       <c r="J36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*J31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*J31*brand_cr_2</f>
         <v/>
       </c>
       <c r="K36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*K31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*K31*brand_cr_2</f>
         <v/>
       </c>
       <c r="L36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*L31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*L31*brand_cr_2</f>
         <v/>
       </c>
       <c r="M36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*M31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*M31*brand_cr_2</f>
         <v/>
       </c>
       <c r="N36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*N31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*N31*brand_cr_2</f>
         <v/>
       </c>
       <c r="O36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*O31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*O31*brand_cr_2</f>
         <v/>
       </c>
       <c r="P36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*P31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*P31*brand_cr_2</f>
         <v/>
       </c>
       <c r="Q36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*Q31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*Q31*brand_cr_2</f>
         <v/>
       </c>
       <c r="R36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*R31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*R31*brand_cr_2</f>
         <v/>
       </c>
       <c r="S36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*S31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*S31*brand_cr_2</f>
         <v/>
       </c>
       <c r="T36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*T31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*T31*brand_cr_2</f>
         <v/>
       </c>
       <c r="U36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*U31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*U31*brand_cr_2</f>
         <v/>
       </c>
       <c r="V36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*V31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*V31*brand_cr_2</f>
         <v/>
       </c>
       <c r="W36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*W31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*W31*brand_cr_2</f>
         <v/>
       </c>
       <c r="X36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*X31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*X31*brand_cr_2</f>
         <v/>
       </c>
       <c r="Y36" s="32">
-        <f>Ввод!$B$11*Ввод!$C$21*Y31*Ввод!$C$22</f>
+        <f>wordstat*brand_share_2*Y31*brand_cr_2</f>
         <v/>
       </c>
     </row>
@@ -4882,99 +4967,99 @@
         </is>
       </c>
       <c r="B37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*B31</f>
+        <f>followers*social_cr_2*B31</f>
         <v/>
       </c>
       <c r="C37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*C31</f>
+        <f>followers*social_cr_2*C31</f>
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*D31</f>
+        <f>followers*social_cr_2*D31</f>
         <v/>
       </c>
       <c r="E37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*E31</f>
+        <f>followers*social_cr_2*E31</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*F31</f>
+        <f>followers*social_cr_2*F31</f>
         <v/>
       </c>
       <c r="G37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*G31</f>
+        <f>followers*social_cr_2*G31</f>
         <v/>
       </c>
       <c r="H37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*H31</f>
+        <f>followers*social_cr_2*H31</f>
         <v/>
       </c>
       <c r="I37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*I31</f>
+        <f>followers*social_cr_2*I31</f>
         <v/>
       </c>
       <c r="J37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*J31</f>
+        <f>followers*social_cr_2*J31</f>
         <v/>
       </c>
       <c r="K37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*K31</f>
+        <f>followers*social_cr_2*K31</f>
         <v/>
       </c>
       <c r="L37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*L31</f>
+        <f>followers*social_cr_2*L31</f>
         <v/>
       </c>
       <c r="M37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*M31</f>
+        <f>followers*social_cr_2*M31</f>
         <v/>
       </c>
       <c r="N37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*N31</f>
+        <f>followers*social_cr_2*N31</f>
         <v/>
       </c>
       <c r="O37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*O31</f>
+        <f>followers*social_cr_2*O31</f>
         <v/>
       </c>
       <c r="P37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*P31</f>
+        <f>followers*social_cr_2*P31</f>
         <v/>
       </c>
       <c r="Q37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*Q31</f>
+        <f>followers*social_cr_2*Q31</f>
         <v/>
       </c>
       <c r="R37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*R31</f>
+        <f>followers*social_cr_2*R31</f>
         <v/>
       </c>
       <c r="S37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*S31</f>
+        <f>followers*social_cr_2*S31</f>
         <v/>
       </c>
       <c r="T37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*T31</f>
+        <f>followers*social_cr_2*T31</f>
         <v/>
       </c>
       <c r="U37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*U31</f>
+        <f>followers*social_cr_2*U31</f>
         <v/>
       </c>
       <c r="V37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*V31</f>
+        <f>followers*social_cr_2*V31</f>
         <v/>
       </c>
       <c r="W37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*W31</f>
+        <f>followers*social_cr_2*W31</f>
         <v/>
       </c>
       <c r="X37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*X31</f>
+        <f>followers*social_cr_2*X31</f>
         <v/>
       </c>
       <c r="Y37" s="32">
-        <f>Ввод!$B$12*Ввод!$C$23*Y31</f>
+        <f>followers*social_cr_2*Y31</f>
         <v/>
       </c>
     </row>
@@ -4985,99 +5070,99 @@
         </is>
       </c>
       <c r="B38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*B31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*B31)</f>
         <v/>
       </c>
       <c r="C38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*C31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*C31)</f>
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*D31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*D31)</f>
         <v/>
       </c>
       <c r="E38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*E31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*E31)</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*F31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*F31)</f>
         <v/>
       </c>
       <c r="G38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*G31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*G31)</f>
         <v/>
       </c>
       <c r="H38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*H31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*H31)</f>
         <v/>
       </c>
       <c r="I38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*I31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*I31)</f>
         <v/>
       </c>
       <c r="J38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*J31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*J31)</f>
         <v/>
       </c>
       <c r="K38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*K31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*K31)</f>
         <v/>
       </c>
       <c r="L38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*L31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*L31)</f>
         <v/>
       </c>
       <c r="M38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*M31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*M31)</f>
         <v/>
       </c>
       <c r="N38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*N31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*N31)</f>
         <v/>
       </c>
       <c r="O38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*O31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*O31)</f>
         <v/>
       </c>
       <c r="P38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*P31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*P31)</f>
         <v/>
       </c>
       <c r="Q38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*Q31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*Q31)</f>
         <v/>
       </c>
       <c r="R38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*R31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*R31)</f>
         <v/>
       </c>
       <c r="S38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*S31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*S31)</f>
         <v/>
       </c>
       <c r="T38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*T31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*T31)</f>
         <v/>
       </c>
       <c r="U38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*U31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*U31)</f>
         <v/>
       </c>
       <c r="V38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*V31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*V31)</f>
         <v/>
       </c>
       <c r="W38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*W31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*W31)</f>
         <v/>
       </c>
       <c r="X38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*X31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*X31)</f>
         <v/>
       </c>
       <c r="Y38" s="32">
-        <f>Ввод!$C$24/Ввод!$C$25*Ввод!$C$26*(0.5+0.5*Y31)</f>
+        <f>ads_budget_2/cpc_2*ads_cr_2*(0.5+0.5*Y31)</f>
         <v/>
       </c>
     </row>
@@ -5191,99 +5276,99 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="C40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="D40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="E40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="F40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="G40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="H40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="I40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="J40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="K40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="L40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="M40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="N40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="O40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="P40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="Q40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="R40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="S40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="T40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="U40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="V40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="W40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="X40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
       <c r="Y40" s="33">
-        <f>Ввод!$B$8*Ввод!$C$27</f>
+        <f>mp_aov*aov_k_2</f>
         <v/>
       </c>
     </row>
@@ -5397,99 +5482,99 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>B41*Ввод!$C$28</f>
+        <f>B41*incr_2</f>
         <v/>
       </c>
       <c r="C42" s="33">
-        <f>C41*Ввод!$C$28</f>
+        <f>C41*incr_2</f>
         <v/>
       </c>
       <c r="D42" s="33">
-        <f>D41*Ввод!$C$28</f>
+        <f>D41*incr_2</f>
         <v/>
       </c>
       <c r="E42" s="33">
-        <f>E41*Ввод!$C$28</f>
+        <f>E41*incr_2</f>
         <v/>
       </c>
       <c r="F42" s="33">
-        <f>F41*Ввод!$C$28</f>
+        <f>F41*incr_2</f>
         <v/>
       </c>
       <c r="G42" s="33">
-        <f>G41*Ввод!$C$28</f>
+        <f>G41*incr_2</f>
         <v/>
       </c>
       <c r="H42" s="33">
-        <f>H41*Ввод!$C$28</f>
+        <f>H41*incr_2</f>
         <v/>
       </c>
       <c r="I42" s="33">
-        <f>I41*Ввод!$C$28</f>
+        <f>I41*incr_2</f>
         <v/>
       </c>
       <c r="J42" s="33">
-        <f>J41*Ввод!$C$28</f>
+        <f>J41*incr_2</f>
         <v/>
       </c>
       <c r="K42" s="33">
-        <f>K41*Ввод!$C$28</f>
+        <f>K41*incr_2</f>
         <v/>
       </c>
       <c r="L42" s="33">
-        <f>L41*Ввод!$C$28</f>
+        <f>L41*incr_2</f>
         <v/>
       </c>
       <c r="M42" s="33">
-        <f>M41*Ввод!$C$28</f>
+        <f>M41*incr_2</f>
         <v/>
       </c>
       <c r="N42" s="33">
-        <f>N41*Ввод!$C$28</f>
+        <f>N41*incr_2</f>
         <v/>
       </c>
       <c r="O42" s="33">
-        <f>O41*Ввод!$C$28</f>
+        <f>O41*incr_2</f>
         <v/>
       </c>
       <c r="P42" s="33">
-        <f>P41*Ввод!$C$28</f>
+        <f>P41*incr_2</f>
         <v/>
       </c>
       <c r="Q42" s="33">
-        <f>Q41*Ввод!$C$28</f>
+        <f>Q41*incr_2</f>
         <v/>
       </c>
       <c r="R42" s="33">
-        <f>R41*Ввод!$C$28</f>
+        <f>R41*incr_2</f>
         <v/>
       </c>
       <c r="S42" s="33">
-        <f>S41*Ввод!$C$28</f>
+        <f>S41*incr_2</f>
         <v/>
       </c>
       <c r="T42" s="33">
-        <f>T41*Ввод!$C$28</f>
+        <f>T41*incr_2</f>
         <v/>
       </c>
       <c r="U42" s="33">
-        <f>U41*Ввод!$C$28</f>
+        <f>U41*incr_2</f>
         <v/>
       </c>
       <c r="V42" s="33">
-        <f>V41*Ввод!$C$28</f>
+        <f>V41*incr_2</f>
         <v/>
       </c>
       <c r="W42" s="33">
-        <f>W41*Ввод!$C$28</f>
+        <f>W41*incr_2</f>
         <v/>
       </c>
       <c r="X42" s="33">
-        <f>X41*Ввод!$C$28</f>
+        <f>X41*incr_2</f>
         <v/>
       </c>
       <c r="Y42" s="33">
-        <f>Y41*Ввод!$C$28</f>
+        <f>Y41*incr_2</f>
         <v/>
       </c>
     </row>
@@ -5603,99 +5688,99 @@
         </is>
       </c>
       <c r="B44" s="35">
-        <f>B41/(Ввод!$B$7-B43+B41)</f>
+        <f>B41/(mp_rev-B43+B41)</f>
         <v/>
       </c>
       <c r="C44" s="35">
-        <f>C41/(Ввод!$B$7-C43+C41)</f>
+        <f>C41/(mp_rev-C43+C41)</f>
         <v/>
       </c>
       <c r="D44" s="35">
-        <f>D41/(Ввод!$B$7-D43+D41)</f>
+        <f>D41/(mp_rev-D43+D41)</f>
         <v/>
       </c>
       <c r="E44" s="35">
-        <f>E41/(Ввод!$B$7-E43+E41)</f>
+        <f>E41/(mp_rev-E43+E41)</f>
         <v/>
       </c>
       <c r="F44" s="35">
-        <f>F41/(Ввод!$B$7-F43+F41)</f>
+        <f>F41/(mp_rev-F43+F41)</f>
         <v/>
       </c>
       <c r="G44" s="35">
-        <f>G41/(Ввод!$B$7-G43+G41)</f>
+        <f>G41/(mp_rev-G43+G41)</f>
         <v/>
       </c>
       <c r="H44" s="35">
-        <f>H41/(Ввод!$B$7-H43+H41)</f>
+        <f>H41/(mp_rev-H43+H41)</f>
         <v/>
       </c>
       <c r="I44" s="35">
-        <f>I41/(Ввод!$B$7-I43+I41)</f>
+        <f>I41/(mp_rev-I43+I41)</f>
         <v/>
       </c>
       <c r="J44" s="35">
-        <f>J41/(Ввод!$B$7-J43+J41)</f>
+        <f>J41/(mp_rev-J43+J41)</f>
         <v/>
       </c>
       <c r="K44" s="35">
-        <f>K41/(Ввод!$B$7-K43+K41)</f>
+        <f>K41/(mp_rev-K43+K41)</f>
         <v/>
       </c>
       <c r="L44" s="35">
-        <f>L41/(Ввод!$B$7-L43+L41)</f>
+        <f>L41/(mp_rev-L43+L41)</f>
         <v/>
       </c>
       <c r="M44" s="35">
-        <f>M41/(Ввод!$B$7-M43+M41)</f>
+        <f>M41/(mp_rev-M43+M41)</f>
         <v/>
       </c>
       <c r="N44" s="35">
-        <f>N41/(Ввод!$B$7-N43+N41)</f>
+        <f>N41/(mp_rev-N43+N41)</f>
         <v/>
       </c>
       <c r="O44" s="35">
-        <f>O41/(Ввод!$B$7-O43+O41)</f>
+        <f>O41/(mp_rev-O43+O41)</f>
         <v/>
       </c>
       <c r="P44" s="35">
-        <f>P41/(Ввод!$B$7-P43+P41)</f>
+        <f>P41/(mp_rev-P43+P41)</f>
         <v/>
       </c>
       <c r="Q44" s="35">
-        <f>Q41/(Ввод!$B$7-Q43+Q41)</f>
+        <f>Q41/(mp_rev-Q43+Q41)</f>
         <v/>
       </c>
       <c r="R44" s="35">
-        <f>R41/(Ввод!$B$7-R43+R41)</f>
+        <f>R41/(mp_rev-R43+R41)</f>
         <v/>
       </c>
       <c r="S44" s="35">
-        <f>S41/(Ввод!$B$7-S43+S41)</f>
+        <f>S41/(mp_rev-S43+S41)</f>
         <v/>
       </c>
       <c r="T44" s="35">
-        <f>T41/(Ввод!$B$7-T43+T41)</f>
+        <f>T41/(mp_rev-T43+T41)</f>
         <v/>
       </c>
       <c r="U44" s="35">
-        <f>U41/(Ввод!$B$7-U43+U41)</f>
+        <f>U41/(mp_rev-U43+U41)</f>
         <v/>
       </c>
       <c r="V44" s="35">
-        <f>V41/(Ввод!$B$7-V43+V41)</f>
+        <f>V41/(mp_rev-V43+V41)</f>
         <v/>
       </c>
       <c r="W44" s="35">
-        <f>W41/(Ввод!$B$7-W43+W41)</f>
+        <f>W41/(mp_rev-W43+W41)</f>
         <v/>
       </c>
       <c r="X44" s="35">
-        <f>X41/(Ввод!$B$7-X43+X41)</f>
+        <f>X41/(mp_rev-X43+X41)</f>
         <v/>
       </c>
       <c r="Y44" s="35">
-        <f>Y41/(Ввод!$B$7-Y43+Y41)</f>
+        <f>Y41/(mp_rev-Y43+Y41)</f>
         <v/>
       </c>
     </row>
@@ -5706,99 +5791,99 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>B41*Ввод!$B$32+B39*(Ввод!$B$33+Ввод!$B$34)+B35*B40*Ввод!$B$35+B36*B40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>B41*acq+B39*(ship+pick)+B35*B40*crm_pct+B36*B40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="C45" s="33">
-        <f>C41*Ввод!$B$32+C39*(Ввод!$B$33+Ввод!$B$34)+C35*C40*Ввод!$B$35+C36*C40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>C41*acq+C39*(ship+pick)+C35*C40*crm_pct+C36*C40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="D45" s="33">
-        <f>D41*Ввод!$B$32+D39*(Ввод!$B$33+Ввод!$B$34)+D35*D40*Ввод!$B$35+D36*D40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>D41*acq+D39*(ship+pick)+D35*D40*crm_pct+D36*D40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="E45" s="33">
-        <f>E41*Ввод!$B$32+E39*(Ввод!$B$33+Ввод!$B$34)+E35*E40*Ввод!$B$35+E36*E40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>E41*acq+E39*(ship+pick)+E35*E40*crm_pct+E36*E40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="F45" s="33">
-        <f>F41*Ввод!$B$32+F39*(Ввод!$B$33+Ввод!$B$34)+F35*F40*Ввод!$B$35+F36*F40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>F41*acq+F39*(ship+pick)+F35*F40*crm_pct+F36*F40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="G45" s="33">
-        <f>G41*Ввод!$B$32+G39*(Ввод!$B$33+Ввод!$B$34)+G35*G40*Ввод!$B$35+G36*G40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>G41*acq+G39*(ship+pick)+G35*G40*crm_pct+G36*G40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="H45" s="33">
-        <f>H41*Ввод!$B$32+H39*(Ввод!$B$33+Ввод!$B$34)+H35*H40*Ввод!$B$35+H36*H40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>H41*acq+H39*(ship+pick)+H35*H40*crm_pct+H36*H40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="I45" s="33">
-        <f>I41*Ввод!$B$32+I39*(Ввод!$B$33+Ввод!$B$34)+I35*I40*Ввод!$B$35+I36*I40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>I41*acq+I39*(ship+pick)+I35*I40*crm_pct+I36*I40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="J45" s="33">
-        <f>J41*Ввод!$B$32+J39*(Ввод!$B$33+Ввод!$B$34)+J35*J40*Ввод!$B$35+J36*J40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>J41*acq+J39*(ship+pick)+J35*J40*crm_pct+J36*J40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="K45" s="33">
-        <f>K41*Ввод!$B$32+K39*(Ввод!$B$33+Ввод!$B$34)+K35*K40*Ввод!$B$35+K36*K40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>K41*acq+K39*(ship+pick)+K35*K40*crm_pct+K36*K40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="L45" s="33">
-        <f>L41*Ввод!$B$32+L39*(Ввод!$B$33+Ввод!$B$34)+L35*L40*Ввод!$B$35+L36*L40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>L41*acq+L39*(ship+pick)+L35*L40*crm_pct+L36*L40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="M45" s="33">
-        <f>M41*Ввод!$B$32+M39*(Ввод!$B$33+Ввод!$B$34)+M35*M40*Ввод!$B$35+M36*M40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>M41*acq+M39*(ship+pick)+M35*M40*crm_pct+M36*M40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="N45" s="33">
-        <f>N41*Ввод!$B$32+N39*(Ввод!$B$33+Ввод!$B$34)+N35*N40*Ввод!$B$35+N36*N40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>N41*acq+N39*(ship+pick)+N35*N40*crm_pct+N36*N40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="O45" s="33">
-        <f>O41*Ввод!$B$32+O39*(Ввод!$B$33+Ввод!$B$34)+O35*O40*Ввод!$B$35+O36*O40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>O41*acq+O39*(ship+pick)+O35*O40*crm_pct+O36*O40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="P45" s="33">
-        <f>P41*Ввод!$B$32+P39*(Ввод!$B$33+Ввод!$B$34)+P35*P40*Ввод!$B$35+P36*P40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>P41*acq+P39*(ship+pick)+P35*P40*crm_pct+P36*P40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="Q45" s="33">
-        <f>Q41*Ввод!$B$32+Q39*(Ввод!$B$33+Ввод!$B$34)+Q35*Q40*Ввод!$B$35+Q36*Q40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>Q41*acq+Q39*(ship+pick)+Q35*Q40*crm_pct+Q36*Q40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="R45" s="33">
-        <f>R41*Ввод!$B$32+R39*(Ввод!$B$33+Ввод!$B$34)+R35*R40*Ввод!$B$35+R36*R40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>R41*acq+R39*(ship+pick)+R35*R40*crm_pct+R36*R40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="S45" s="33">
-        <f>S41*Ввод!$B$32+S39*(Ввод!$B$33+Ввод!$B$34)+S35*S40*Ввод!$B$35+S36*S40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>S41*acq+S39*(ship+pick)+S35*S40*crm_pct+S36*S40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="T45" s="33">
-        <f>T41*Ввод!$B$32+T39*(Ввод!$B$33+Ввод!$B$34)+T35*T40*Ввод!$B$35+T36*T40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>T41*acq+T39*(ship+pick)+T35*T40*crm_pct+T36*T40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="U45" s="33">
-        <f>U41*Ввод!$B$32+U39*(Ввод!$B$33+Ввод!$B$34)+U35*U40*Ввод!$B$35+U36*U40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>U41*acq+U39*(ship+pick)+U35*U40*crm_pct+U36*U40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="V45" s="33">
-        <f>V41*Ввод!$B$32+V39*(Ввод!$B$33+Ввод!$B$34)+V35*V40*Ввод!$B$35+V36*V40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>V41*acq+V39*(ship+pick)+V35*V40*crm_pct+V36*V40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="W45" s="33">
-        <f>W41*Ввод!$B$32+W39*(Ввод!$B$33+Ввод!$B$34)+W35*W40*Ввод!$B$35+W36*W40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>W41*acq+W39*(ship+pick)+W35*W40*crm_pct+W36*W40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="X45" s="33">
-        <f>X41*Ввод!$B$32+X39*(Ввод!$B$33+Ввод!$B$34)+X35*X40*Ввод!$B$35+X36*X40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>X41*acq+X39*(ship+pick)+X35*X40*crm_pct+X36*X40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
       <c r="Y45" s="33">
-        <f>Y41*Ввод!$B$32+Y39*(Ввод!$B$33+Ввод!$B$34)+Y35*Y40*Ввод!$B$35+Y36*Y40*Ввод!$B$36+Ввод!$C$24+Ввод!$B$37</f>
+        <f>Y41*acq+Y39*(ship+pick)+Y35*Y40*crm_pct+Y36*Y40*brand_cost+ads_budget_2+platform</f>
         <v/>
       </c>
     </row>
@@ -5912,99 +5997,99 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>Ввод!$B$40+Ввод!$B$41+B41*Ввод!$B$42</f>
+        <f>svc_setup+svc_month+B41*svc_pct</f>
         <v/>
       </c>
       <c r="C47" s="33">
-        <f>Ввод!$B$41+C41*Ввод!$B$42</f>
+        <f>svc_month+C41*svc_pct</f>
         <v/>
       </c>
       <c r="D47" s="33">
-        <f>Ввод!$B$41+D41*Ввод!$B$42</f>
+        <f>svc_month+D41*svc_pct</f>
         <v/>
       </c>
       <c r="E47" s="33">
-        <f>Ввод!$B$41+E41*Ввод!$B$42</f>
+        <f>svc_month+E41*svc_pct</f>
         <v/>
       </c>
       <c r="F47" s="33">
-        <f>Ввод!$B$41+F41*Ввод!$B$42</f>
+        <f>svc_month+F41*svc_pct</f>
         <v/>
       </c>
       <c r="G47" s="33">
-        <f>Ввод!$B$41+G41*Ввод!$B$42</f>
+        <f>svc_month+G41*svc_pct</f>
         <v/>
       </c>
       <c r="H47" s="33">
-        <f>Ввод!$B$41+H41*Ввод!$B$42</f>
+        <f>svc_month+H41*svc_pct</f>
         <v/>
       </c>
       <c r="I47" s="33">
-        <f>Ввод!$B$41+I41*Ввод!$B$42</f>
+        <f>svc_month+I41*svc_pct</f>
         <v/>
       </c>
       <c r="J47" s="33">
-        <f>Ввод!$B$41+J41*Ввод!$B$42</f>
+        <f>svc_month+J41*svc_pct</f>
         <v/>
       </c>
       <c r="K47" s="33">
-        <f>Ввод!$B$41+K41*Ввод!$B$42</f>
+        <f>svc_month+K41*svc_pct</f>
         <v/>
       </c>
       <c r="L47" s="33">
-        <f>Ввод!$B$41+L41*Ввод!$B$42</f>
+        <f>svc_month+L41*svc_pct</f>
         <v/>
       </c>
       <c r="M47" s="33">
-        <f>Ввод!$B$41+M41*Ввод!$B$42</f>
+        <f>svc_month+M41*svc_pct</f>
         <v/>
       </c>
       <c r="N47" s="33">
-        <f>Ввод!$B$41+N41*Ввод!$B$42</f>
+        <f>svc_month+N41*svc_pct</f>
         <v/>
       </c>
       <c r="O47" s="33">
-        <f>Ввод!$B$41+O41*Ввод!$B$42</f>
+        <f>svc_month+O41*svc_pct</f>
         <v/>
       </c>
       <c r="P47" s="33">
-        <f>Ввод!$B$41+P41*Ввод!$B$42</f>
+        <f>svc_month+P41*svc_pct</f>
         <v/>
       </c>
       <c r="Q47" s="33">
-        <f>Ввод!$B$41+Q41*Ввод!$B$42</f>
+        <f>svc_month+Q41*svc_pct</f>
         <v/>
       </c>
       <c r="R47" s="33">
-        <f>Ввод!$B$41+R41*Ввод!$B$42</f>
+        <f>svc_month+R41*svc_pct</f>
         <v/>
       </c>
       <c r="S47" s="33">
-        <f>Ввод!$B$41+S41*Ввод!$B$42</f>
+        <f>svc_month+S41*svc_pct</f>
         <v/>
       </c>
       <c r="T47" s="33">
-        <f>Ввод!$B$41+T41*Ввод!$B$42</f>
+        <f>svc_month+T41*svc_pct</f>
         <v/>
       </c>
       <c r="U47" s="33">
-        <f>Ввод!$B$41+U41*Ввод!$B$42</f>
+        <f>svc_month+U41*svc_pct</f>
         <v/>
       </c>
       <c r="V47" s="33">
-        <f>Ввод!$B$41+V41*Ввод!$B$42</f>
+        <f>svc_month+V41*svc_pct</f>
         <v/>
       </c>
       <c r="W47" s="33">
-        <f>Ввод!$B$41+W41*Ввод!$B$42</f>
+        <f>svc_month+W41*svc_pct</f>
         <v/>
       </c>
       <c r="X47" s="33">
-        <f>Ввод!$B$41+X41*Ввод!$B$42</f>
+        <f>svc_month+X41*svc_pct</f>
         <v/>
       </c>
       <c r="Y47" s="33">
-        <f>Ввод!$B$41+Y41*Ввод!$B$42</f>
+        <f>svc_month+Y41*svc_pct</f>
         <v/>
       </c>
     </row>
@@ -6015,99 +6100,99 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>B41*(1-Ввод!$B$10)-B45-B47</f>
+        <f>B41*(1-cogs)-B45-B47</f>
         <v/>
       </c>
       <c r="C48" s="33">
-        <f>C41*(1-Ввод!$B$10)-C45-C47</f>
+        <f>C41*(1-cogs)-C45-C47</f>
         <v/>
       </c>
       <c r="D48" s="33">
-        <f>D41*(1-Ввод!$B$10)-D45-D47</f>
+        <f>D41*(1-cogs)-D45-D47</f>
         <v/>
       </c>
       <c r="E48" s="33">
-        <f>E41*(1-Ввод!$B$10)-E45-E47</f>
+        <f>E41*(1-cogs)-E45-E47</f>
         <v/>
       </c>
       <c r="F48" s="33">
-        <f>F41*(1-Ввод!$B$10)-F45-F47</f>
+        <f>F41*(1-cogs)-F45-F47</f>
         <v/>
       </c>
       <c r="G48" s="33">
-        <f>G41*(1-Ввод!$B$10)-G45-G47</f>
+        <f>G41*(1-cogs)-G45-G47</f>
         <v/>
       </c>
       <c r="H48" s="33">
-        <f>H41*(1-Ввод!$B$10)-H45-H47</f>
+        <f>H41*(1-cogs)-H45-H47</f>
         <v/>
       </c>
       <c r="I48" s="33">
-        <f>I41*(1-Ввод!$B$10)-I45-I47</f>
+        <f>I41*(1-cogs)-I45-I47</f>
         <v/>
       </c>
       <c r="J48" s="33">
-        <f>J41*(1-Ввод!$B$10)-J45-J47</f>
+        <f>J41*(1-cogs)-J45-J47</f>
         <v/>
       </c>
       <c r="K48" s="33">
-        <f>K41*(1-Ввод!$B$10)-K45-K47</f>
+        <f>K41*(1-cogs)-K45-K47</f>
         <v/>
       </c>
       <c r="L48" s="33">
-        <f>L41*(1-Ввод!$B$10)-L45-L47</f>
+        <f>L41*(1-cogs)-L45-L47</f>
         <v/>
       </c>
       <c r="M48" s="33">
-        <f>M41*(1-Ввод!$B$10)-M45-M47</f>
+        <f>M41*(1-cogs)-M45-M47</f>
         <v/>
       </c>
       <c r="N48" s="33">
-        <f>N41*(1-Ввод!$B$10)-N45-N47</f>
+        <f>N41*(1-cogs)-N45-N47</f>
         <v/>
       </c>
       <c r="O48" s="33">
-        <f>O41*(1-Ввод!$B$10)-O45-O47</f>
+        <f>O41*(1-cogs)-O45-O47</f>
         <v/>
       </c>
       <c r="P48" s="33">
-        <f>P41*(1-Ввод!$B$10)-P45-P47</f>
+        <f>P41*(1-cogs)-P45-P47</f>
         <v/>
       </c>
       <c r="Q48" s="33">
-        <f>Q41*(1-Ввод!$B$10)-Q45-Q47</f>
+        <f>Q41*(1-cogs)-Q45-Q47</f>
         <v/>
       </c>
       <c r="R48" s="33">
-        <f>R41*(1-Ввод!$B$10)-R45-R47</f>
+        <f>R41*(1-cogs)-R45-R47</f>
         <v/>
       </c>
       <c r="S48" s="33">
-        <f>S41*(1-Ввод!$B$10)-S45-S47</f>
+        <f>S41*(1-cogs)-S45-S47</f>
         <v/>
       </c>
       <c r="T48" s="33">
-        <f>T41*(1-Ввод!$B$10)-T45-T47</f>
+        <f>T41*(1-cogs)-T45-T47</f>
         <v/>
       </c>
       <c r="U48" s="33">
-        <f>U41*(1-Ввод!$B$10)-U45-U47</f>
+        <f>U41*(1-cogs)-U45-U47</f>
         <v/>
       </c>
       <c r="V48" s="33">
-        <f>V41*(1-Ввод!$B$10)-V45-V47</f>
+        <f>V41*(1-cogs)-V45-V47</f>
         <v/>
       </c>
       <c r="W48" s="33">
-        <f>W41*(1-Ввод!$B$10)-W45-W47</f>
+        <f>W41*(1-cogs)-W45-W47</f>
         <v/>
       </c>
       <c r="X48" s="33">
-        <f>X41*(1-Ввод!$B$10)-X45-X47</f>
+        <f>X41*(1-cogs)-X45-X47</f>
         <v/>
       </c>
       <c r="Y48" s="33">
-        <f>Y41*(1-Ввод!$B$10)-Y45-Y47</f>
+        <f>Y41*(1-cogs)-Y45-Y47</f>
         <v/>
       </c>
     </row>
@@ -6118,99 +6203,99 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>B43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>B43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="C49" s="33">
-        <f>C43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>C43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="D49" s="33">
-        <f>D43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>D43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="E49" s="33">
-        <f>E43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>E43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="F49" s="33">
-        <f>F43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>F43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="G49" s="33">
-        <f>G43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>G43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="H49" s="33">
-        <f>H43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>H43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="I49" s="33">
-        <f>I43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>I43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="J49" s="33">
-        <f>J43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>J43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="K49" s="33">
-        <f>K43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>K43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="L49" s="33">
-        <f>L43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>L43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="M49" s="33">
-        <f>M43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>M43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="N49" s="33">
-        <f>N43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>N43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="O49" s="33">
-        <f>O43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>O43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="P49" s="33">
-        <f>P43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>P43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Q49" s="33">
-        <f>Q43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Q43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="R49" s="33">
-        <f>R43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>R43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="S49" s="33">
-        <f>S43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>S43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="T49" s="33">
-        <f>T43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>T43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="U49" s="33">
-        <f>U43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>U43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="V49" s="33">
-        <f>V43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>V43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="W49" s="33">
-        <f>W43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>W43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="X49" s="33">
-        <f>X43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>X43*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Y49" s="33">
-        <f>Y43*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Y43*(1-cogs-mp_take)</f>
         <v/>
       </c>
     </row>
@@ -6667,99 +6752,99 @@
         </is>
       </c>
       <c r="B56" s="30">
-        <f>MIN(1,B55/Ввод!$D$29)</f>
+        <f>MIN(1,B55/ramp_3)</f>
         <v/>
       </c>
       <c r="C56" s="30">
-        <f>MIN(1,C55/Ввод!$D$29)</f>
+        <f>MIN(1,C55/ramp_3)</f>
         <v/>
       </c>
       <c r="D56" s="30">
-        <f>MIN(1,D55/Ввод!$D$29)</f>
+        <f>MIN(1,D55/ramp_3)</f>
         <v/>
       </c>
       <c r="E56" s="30">
-        <f>MIN(1,E55/Ввод!$D$29)</f>
+        <f>MIN(1,E55/ramp_3)</f>
         <v/>
       </c>
       <c r="F56" s="30">
-        <f>MIN(1,F55/Ввод!$D$29)</f>
+        <f>MIN(1,F55/ramp_3)</f>
         <v/>
       </c>
       <c r="G56" s="30">
-        <f>MIN(1,G55/Ввод!$D$29)</f>
+        <f>MIN(1,G55/ramp_3)</f>
         <v/>
       </c>
       <c r="H56" s="30">
-        <f>MIN(1,H55/Ввод!$D$29)</f>
+        <f>MIN(1,H55/ramp_3)</f>
         <v/>
       </c>
       <c r="I56" s="30">
-        <f>MIN(1,I55/Ввод!$D$29)</f>
+        <f>MIN(1,I55/ramp_3)</f>
         <v/>
       </c>
       <c r="J56" s="30">
-        <f>MIN(1,J55/Ввод!$D$29)</f>
+        <f>MIN(1,J55/ramp_3)</f>
         <v/>
       </c>
       <c r="K56" s="30">
-        <f>MIN(1,K55/Ввод!$D$29)</f>
+        <f>MIN(1,K55/ramp_3)</f>
         <v/>
       </c>
       <c r="L56" s="30">
-        <f>MIN(1,L55/Ввод!$D$29)</f>
+        <f>MIN(1,L55/ramp_3)</f>
         <v/>
       </c>
       <c r="M56" s="30">
-        <f>MIN(1,M55/Ввод!$D$29)</f>
+        <f>MIN(1,M55/ramp_3)</f>
         <v/>
       </c>
       <c r="N56" s="30">
-        <f>MIN(1,N55/Ввод!$D$29)</f>
+        <f>MIN(1,N55/ramp_3)</f>
         <v/>
       </c>
       <c r="O56" s="30">
-        <f>MIN(1,O55/Ввод!$D$29)</f>
+        <f>MIN(1,O55/ramp_3)</f>
         <v/>
       </c>
       <c r="P56" s="30">
-        <f>MIN(1,P55/Ввод!$D$29)</f>
+        <f>MIN(1,P55/ramp_3)</f>
         <v/>
       </c>
       <c r="Q56" s="30">
-        <f>MIN(1,Q55/Ввод!$D$29)</f>
+        <f>MIN(1,Q55/ramp_3)</f>
         <v/>
       </c>
       <c r="R56" s="30">
-        <f>MIN(1,R55/Ввод!$D$29)</f>
+        <f>MIN(1,R55/ramp_3)</f>
         <v/>
       </c>
       <c r="S56" s="30">
-        <f>MIN(1,S55/Ввод!$D$29)</f>
+        <f>MIN(1,S55/ramp_3)</f>
         <v/>
       </c>
       <c r="T56" s="30">
-        <f>MIN(1,T55/Ввод!$D$29)</f>
+        <f>MIN(1,T55/ramp_3)</f>
         <v/>
       </c>
       <c r="U56" s="30">
-        <f>MIN(1,U55/Ввод!$D$29)</f>
+        <f>MIN(1,U55/ramp_3)</f>
         <v/>
       </c>
       <c r="V56" s="30">
-        <f>MIN(1,V55/Ввод!$D$29)</f>
+        <f>MIN(1,V55/ramp_3)</f>
         <v/>
       </c>
       <c r="W56" s="30">
-        <f>MIN(1,W55/Ввод!$D$29)</f>
+        <f>MIN(1,W55/ramp_3)</f>
         <v/>
       </c>
       <c r="X56" s="30">
-        <f>MIN(1,X55/Ввод!$D$29)</f>
+        <f>MIN(1,X55/ramp_3)</f>
         <v/>
       </c>
       <c r="Y56" s="30">
-        <f>MIN(1,Y55/Ввод!$D$29)</f>
+        <f>MIN(1,Y55/ramp_3)</f>
         <v/>
       </c>
     </row>
@@ -6770,202 +6855,202 @@
         </is>
       </c>
       <c r="B57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="C57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="D57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="E57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="F57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="G57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="H57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="I57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="J57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="K57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="L57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="M57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="N57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="O57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="P57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Q57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="R57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="S57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="T57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="U57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="V57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="W57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="X57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
       <c r="Y57" s="31">
-        <f>Ввод!$B$7/Ввод!$B$8</f>
+        <f>mp_rev/mp_aov</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Новых людей в базе</t>
+          <t>Новых людей в базе (с МП + новые покупатели сайта)</t>
         </is>
       </c>
       <c r="B58" s="31">
-        <f>B57*Ввод!$D$19*B56</f>
+        <f>B57*conv_base_3*B56+B61+B62+B63</f>
         <v/>
       </c>
       <c r="C58" s="31">
-        <f>C57*Ввод!$D$19*C56</f>
+        <f>C57*conv_base_3*C56+C61+C62+C63</f>
         <v/>
       </c>
       <c r="D58" s="31">
-        <f>D57*Ввод!$D$19*D56</f>
+        <f>D57*conv_base_3*D56+D61+D62+D63</f>
         <v/>
       </c>
       <c r="E58" s="31">
-        <f>E57*Ввод!$D$19*E56</f>
+        <f>E57*conv_base_3*E56+E61+E62+E63</f>
         <v/>
       </c>
       <c r="F58" s="31">
-        <f>F57*Ввод!$D$19*F56</f>
+        <f>F57*conv_base_3*F56+F61+F62+F63</f>
         <v/>
       </c>
       <c r="G58" s="31">
-        <f>G57*Ввод!$D$19*G56</f>
+        <f>G57*conv_base_3*G56+G61+G62+G63</f>
         <v/>
       </c>
       <c r="H58" s="31">
-        <f>H57*Ввод!$D$19*H56</f>
+        <f>H57*conv_base_3*H56+H61+H62+H63</f>
         <v/>
       </c>
       <c r="I58" s="31">
-        <f>I57*Ввод!$D$19*I56</f>
+        <f>I57*conv_base_3*I56+I61+I62+I63</f>
         <v/>
       </c>
       <c r="J58" s="31">
-        <f>J57*Ввод!$D$19*J56</f>
+        <f>J57*conv_base_3*J56+J61+J62+J63</f>
         <v/>
       </c>
       <c r="K58" s="31">
-        <f>K57*Ввод!$D$19*K56</f>
+        <f>K57*conv_base_3*K56+K61+K62+K63</f>
         <v/>
       </c>
       <c r="L58" s="31">
-        <f>L57*Ввод!$D$19*L56</f>
+        <f>L57*conv_base_3*L56+L61+L62+L63</f>
         <v/>
       </c>
       <c r="M58" s="31">
-        <f>M57*Ввод!$D$19*M56</f>
+        <f>M57*conv_base_3*M56+M61+M62+M63</f>
         <v/>
       </c>
       <c r="N58" s="31">
-        <f>N57*Ввод!$D$19*N56</f>
+        <f>N57*conv_base_3*N56+N61+N62+N63</f>
         <v/>
       </c>
       <c r="O58" s="31">
-        <f>O57*Ввод!$D$19*O56</f>
+        <f>O57*conv_base_3*O56+O61+O62+O63</f>
         <v/>
       </c>
       <c r="P58" s="31">
-        <f>P57*Ввод!$D$19*P56</f>
+        <f>P57*conv_base_3*P56+P61+P62+P63</f>
         <v/>
       </c>
       <c r="Q58" s="31">
-        <f>Q57*Ввод!$D$19*Q56</f>
+        <f>Q57*conv_base_3*Q56+Q61+Q62+Q63</f>
         <v/>
       </c>
       <c r="R58" s="31">
-        <f>R57*Ввод!$D$19*R56</f>
+        <f>R57*conv_base_3*R56+R61+R62+R63</f>
         <v/>
       </c>
       <c r="S58" s="31">
-        <f>S57*Ввод!$D$19*S56</f>
+        <f>S57*conv_base_3*S56+S61+S62+S63</f>
         <v/>
       </c>
       <c r="T58" s="31">
-        <f>T57*Ввод!$D$19*T56</f>
+        <f>T57*conv_base_3*T56+T61+T62+T63</f>
         <v/>
       </c>
       <c r="U58" s="31">
-        <f>U57*Ввод!$D$19*U56</f>
+        <f>U57*conv_base_3*U56+U61+U62+U63</f>
         <v/>
       </c>
       <c r="V58" s="31">
-        <f>V57*Ввод!$D$19*V56</f>
+        <f>V57*conv_base_3*V56+V61+V62+V63</f>
         <v/>
       </c>
       <c r="W58" s="31">
-        <f>W57*Ввод!$D$19*W56</f>
+        <f>W57*conv_base_3*W56+W61+W62+W63</f>
         <v/>
       </c>
       <c r="X58" s="31">
-        <f>X57*Ввод!$D$19*X56</f>
+        <f>X57*conv_base_3*X56+X61+X62+X63</f>
         <v/>
       </c>
       <c r="Y58" s="31">
-        <f>Y57*Ввод!$D$19*Y56</f>
+        <f>Y57*conv_base_3*Y56+Y61+Y62+Y63</f>
         <v/>
       </c>
     </row>
@@ -6980,95 +7065,95 @@
         <v/>
       </c>
       <c r="C59" s="31">
-        <f>B59+C58</f>
+        <f>B59*(1-churn_3)+C58</f>
         <v/>
       </c>
       <c r="D59" s="31">
-        <f>C59+D58</f>
+        <f>C59*(1-churn_3)+D58</f>
         <v/>
       </c>
       <c r="E59" s="31">
-        <f>D59+E58</f>
+        <f>D59*(1-churn_3)+E58</f>
         <v/>
       </c>
       <c r="F59" s="31">
-        <f>E59+F58</f>
+        <f>E59*(1-churn_3)+F58</f>
         <v/>
       </c>
       <c r="G59" s="31">
-        <f>F59+G58</f>
+        <f>F59*(1-churn_3)+G58</f>
         <v/>
       </c>
       <c r="H59" s="31">
-        <f>G59+H58</f>
+        <f>G59*(1-churn_3)+H58</f>
         <v/>
       </c>
       <c r="I59" s="31">
-        <f>H59+I58</f>
+        <f>H59*(1-churn_3)+I58</f>
         <v/>
       </c>
       <c r="J59" s="31">
-        <f>I59+J58</f>
+        <f>I59*(1-churn_3)+J58</f>
         <v/>
       </c>
       <c r="K59" s="31">
-        <f>J59+K58</f>
+        <f>J59*(1-churn_3)+K58</f>
         <v/>
       </c>
       <c r="L59" s="31">
-        <f>K59+L58</f>
+        <f>K59*(1-churn_3)+L58</f>
         <v/>
       </c>
       <c r="M59" s="31">
-        <f>L59+M58</f>
+        <f>L59*(1-churn_3)+M58</f>
         <v/>
       </c>
       <c r="N59" s="31">
-        <f>M59+N58</f>
+        <f>M59*(1-churn_3)+N58</f>
         <v/>
       </c>
       <c r="O59" s="31">
-        <f>N59+O58</f>
+        <f>N59*(1-churn_3)+O58</f>
         <v/>
       </c>
       <c r="P59" s="31">
-        <f>O59+P58</f>
+        <f>O59*(1-churn_3)+P58</f>
         <v/>
       </c>
       <c r="Q59" s="31">
-        <f>P59+Q58</f>
+        <f>P59*(1-churn_3)+Q58</f>
         <v/>
       </c>
       <c r="R59" s="31">
-        <f>Q59+R58</f>
+        <f>Q59*(1-churn_3)+R58</f>
         <v/>
       </c>
       <c r="S59" s="31">
-        <f>R59+S58</f>
+        <f>R59*(1-churn_3)+S58</f>
         <v/>
       </c>
       <c r="T59" s="31">
-        <f>S59+T58</f>
+        <f>S59*(1-churn_3)+T58</f>
         <v/>
       </c>
       <c r="U59" s="31">
-        <f>T59+U58</f>
+        <f>T59*(1-churn_3)+U58</f>
         <v/>
       </c>
       <c r="V59" s="31">
-        <f>U59+V58</f>
+        <f>U59*(1-churn_3)+V58</f>
         <v/>
       </c>
       <c r="W59" s="31">
-        <f>V59+W58</f>
+        <f>V59*(1-churn_3)+W58</f>
         <v/>
       </c>
       <c r="X59" s="31">
-        <f>W59+X58</f>
+        <f>W59*(1-churn_3)+X58</f>
         <v/>
       </c>
       <c r="Y59" s="31">
-        <f>X59+Y58</f>
+        <f>X59*(1-churn_3)+Y58</f>
         <v/>
       </c>
     </row>
@@ -7079,99 +7164,99 @@
         </is>
       </c>
       <c r="B60" s="32">
-        <f>0*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>0*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="C60" s="32">
-        <f>B59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>B59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="D60" s="32">
-        <f>C59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>C59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="E60" s="32">
-        <f>D59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>D59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="F60" s="32">
-        <f>E59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>E59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="G60" s="32">
-        <f>F59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>F59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="H60" s="32">
-        <f>G59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>G59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="I60" s="32">
-        <f>H59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>H59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="J60" s="32">
-        <f>I59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>I59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="K60" s="32">
-        <f>J59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>J59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="L60" s="32">
-        <f>K59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>K59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="M60" s="32">
-        <f>L59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>L59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="N60" s="32">
-        <f>M59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>M59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="O60" s="32">
-        <f>N59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>N59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="P60" s="32">
-        <f>O59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>O59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="Q60" s="32">
-        <f>P59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>P59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="R60" s="32">
-        <f>Q59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>Q59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="S60" s="32">
-        <f>R59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>R59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="T60" s="32">
-        <f>S59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>S59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="U60" s="32">
-        <f>T59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>T59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="V60" s="32">
-        <f>U59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>U59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="W60" s="32">
-        <f>V59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>V59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="X60" s="32">
-        <f>W59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>W59*freq/12*base_site_3</f>
         <v/>
       </c>
       <c r="Y60" s="32">
-        <f>X59*Ввод!$B$13/12*Ввод!$D$20</f>
+        <f>X59*freq/12*base_site_3</f>
         <v/>
       </c>
     </row>
@@ -7182,99 +7267,99 @@
         </is>
       </c>
       <c r="B61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*B56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*B56*brand_cr_3</f>
         <v/>
       </c>
       <c r="C61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*C56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*C56*brand_cr_3</f>
         <v/>
       </c>
       <c r="D61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*D56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*D56*brand_cr_3</f>
         <v/>
       </c>
       <c r="E61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*E56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*E56*brand_cr_3</f>
         <v/>
       </c>
       <c r="F61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*F56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*F56*brand_cr_3</f>
         <v/>
       </c>
       <c r="G61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*G56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*G56*brand_cr_3</f>
         <v/>
       </c>
       <c r="H61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*H56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*H56*brand_cr_3</f>
         <v/>
       </c>
       <c r="I61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*I56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*I56*brand_cr_3</f>
         <v/>
       </c>
       <c r="J61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*J56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*J56*brand_cr_3</f>
         <v/>
       </c>
       <c r="K61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*K56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*K56*brand_cr_3</f>
         <v/>
       </c>
       <c r="L61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*L56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*L56*brand_cr_3</f>
         <v/>
       </c>
       <c r="M61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*M56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*M56*brand_cr_3</f>
         <v/>
       </c>
       <c r="N61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*N56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*N56*brand_cr_3</f>
         <v/>
       </c>
       <c r="O61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*O56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*O56*brand_cr_3</f>
         <v/>
       </c>
       <c r="P61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*P56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*P56*brand_cr_3</f>
         <v/>
       </c>
       <c r="Q61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*Q56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*Q56*brand_cr_3</f>
         <v/>
       </c>
       <c r="R61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*R56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*R56*brand_cr_3</f>
         <v/>
       </c>
       <c r="S61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*S56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*S56*brand_cr_3</f>
         <v/>
       </c>
       <c r="T61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*T56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*T56*brand_cr_3</f>
         <v/>
       </c>
       <c r="U61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*U56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*U56*brand_cr_3</f>
         <v/>
       </c>
       <c r="V61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*V56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*V56*brand_cr_3</f>
         <v/>
       </c>
       <c r="W61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*W56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*W56*brand_cr_3</f>
         <v/>
       </c>
       <c r="X61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*X56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*X56*brand_cr_3</f>
         <v/>
       </c>
       <c r="Y61" s="32">
-        <f>Ввод!$B$11*Ввод!$D$21*Y56*Ввод!$D$22</f>
+        <f>wordstat*brand_share_3*Y56*brand_cr_3</f>
         <v/>
       </c>
     </row>
@@ -7285,99 +7370,99 @@
         </is>
       </c>
       <c r="B62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*B56</f>
+        <f>followers*social_cr_3*B56</f>
         <v/>
       </c>
       <c r="C62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*C56</f>
+        <f>followers*social_cr_3*C56</f>
         <v/>
       </c>
       <c r="D62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*D56</f>
+        <f>followers*social_cr_3*D56</f>
         <v/>
       </c>
       <c r="E62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*E56</f>
+        <f>followers*social_cr_3*E56</f>
         <v/>
       </c>
       <c r="F62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*F56</f>
+        <f>followers*social_cr_3*F56</f>
         <v/>
       </c>
       <c r="G62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*G56</f>
+        <f>followers*social_cr_3*G56</f>
         <v/>
       </c>
       <c r="H62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*H56</f>
+        <f>followers*social_cr_3*H56</f>
         <v/>
       </c>
       <c r="I62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*I56</f>
+        <f>followers*social_cr_3*I56</f>
         <v/>
       </c>
       <c r="J62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*J56</f>
+        <f>followers*social_cr_3*J56</f>
         <v/>
       </c>
       <c r="K62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*K56</f>
+        <f>followers*social_cr_3*K56</f>
         <v/>
       </c>
       <c r="L62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*L56</f>
+        <f>followers*social_cr_3*L56</f>
         <v/>
       </c>
       <c r="M62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*M56</f>
+        <f>followers*social_cr_3*M56</f>
         <v/>
       </c>
       <c r="N62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*N56</f>
+        <f>followers*social_cr_3*N56</f>
         <v/>
       </c>
       <c r="O62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*O56</f>
+        <f>followers*social_cr_3*O56</f>
         <v/>
       </c>
       <c r="P62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*P56</f>
+        <f>followers*social_cr_3*P56</f>
         <v/>
       </c>
       <c r="Q62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*Q56</f>
+        <f>followers*social_cr_3*Q56</f>
         <v/>
       </c>
       <c r="R62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*R56</f>
+        <f>followers*social_cr_3*R56</f>
         <v/>
       </c>
       <c r="S62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*S56</f>
+        <f>followers*social_cr_3*S56</f>
         <v/>
       </c>
       <c r="T62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*T56</f>
+        <f>followers*social_cr_3*T56</f>
         <v/>
       </c>
       <c r="U62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*U56</f>
+        <f>followers*social_cr_3*U56</f>
         <v/>
       </c>
       <c r="V62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*V56</f>
+        <f>followers*social_cr_3*V56</f>
         <v/>
       </c>
       <c r="W62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*W56</f>
+        <f>followers*social_cr_3*W56</f>
         <v/>
       </c>
       <c r="X62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*X56</f>
+        <f>followers*social_cr_3*X56</f>
         <v/>
       </c>
       <c r="Y62" s="32">
-        <f>Ввод!$B$12*Ввод!$D$23*Y56</f>
+        <f>followers*social_cr_3*Y56</f>
         <v/>
       </c>
     </row>
@@ -7388,99 +7473,99 @@
         </is>
       </c>
       <c r="B63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*B56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*B56)</f>
         <v/>
       </c>
       <c r="C63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*C56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*C56)</f>
         <v/>
       </c>
       <c r="D63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*D56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*D56)</f>
         <v/>
       </c>
       <c r="E63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*E56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*E56)</f>
         <v/>
       </c>
       <c r="F63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*F56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*F56)</f>
         <v/>
       </c>
       <c r="G63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*G56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*G56)</f>
         <v/>
       </c>
       <c r="H63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*H56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*H56)</f>
         <v/>
       </c>
       <c r="I63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*I56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*I56)</f>
         <v/>
       </c>
       <c r="J63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*J56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*J56)</f>
         <v/>
       </c>
       <c r="K63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*K56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*K56)</f>
         <v/>
       </c>
       <c r="L63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*L56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*L56)</f>
         <v/>
       </c>
       <c r="M63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*M56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*M56)</f>
         <v/>
       </c>
       <c r="N63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*N56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*N56)</f>
         <v/>
       </c>
       <c r="O63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*O56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*O56)</f>
         <v/>
       </c>
       <c r="P63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*P56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*P56)</f>
         <v/>
       </c>
       <c r="Q63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*Q56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*Q56)</f>
         <v/>
       </c>
       <c r="R63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*R56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*R56)</f>
         <v/>
       </c>
       <c r="S63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*S56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*S56)</f>
         <v/>
       </c>
       <c r="T63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*T56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*T56)</f>
         <v/>
       </c>
       <c r="U63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*U56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*U56)</f>
         <v/>
       </c>
       <c r="V63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*V56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*V56)</f>
         <v/>
       </c>
       <c r="W63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*W56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*W56)</f>
         <v/>
       </c>
       <c r="X63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*X56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*X56)</f>
         <v/>
       </c>
       <c r="Y63" s="32">
-        <f>Ввод!$D$24/Ввод!$D$25*Ввод!$D$26*(0.5+0.5*Y56)</f>
+        <f>ads_budget_3/cpc_3*ads_cr_3*(0.5+0.5*Y56)</f>
         <v/>
       </c>
     </row>
@@ -7594,99 +7679,99 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="C65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="D65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="E65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="F65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="G65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="H65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="I65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="J65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="K65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="L65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="M65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="N65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="O65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="P65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="Q65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="R65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="S65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="T65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="U65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="V65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="W65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="X65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
       <c r="Y65" s="33">
-        <f>Ввод!$B$8*Ввод!$D$27</f>
+        <f>mp_aov*aov_k_3</f>
         <v/>
       </c>
     </row>
@@ -7800,99 +7885,99 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>B66*Ввод!$D$28</f>
+        <f>B66*incr_3</f>
         <v/>
       </c>
       <c r="C67" s="33">
-        <f>C66*Ввод!$D$28</f>
+        <f>C66*incr_3</f>
         <v/>
       </c>
       <c r="D67" s="33">
-        <f>D66*Ввод!$D$28</f>
+        <f>D66*incr_3</f>
         <v/>
       </c>
       <c r="E67" s="33">
-        <f>E66*Ввод!$D$28</f>
+        <f>E66*incr_3</f>
         <v/>
       </c>
       <c r="F67" s="33">
-        <f>F66*Ввод!$D$28</f>
+        <f>F66*incr_3</f>
         <v/>
       </c>
       <c r="G67" s="33">
-        <f>G66*Ввод!$D$28</f>
+        <f>G66*incr_3</f>
         <v/>
       </c>
       <c r="H67" s="33">
-        <f>H66*Ввод!$D$28</f>
+        <f>H66*incr_3</f>
         <v/>
       </c>
       <c r="I67" s="33">
-        <f>I66*Ввод!$D$28</f>
+        <f>I66*incr_3</f>
         <v/>
       </c>
       <c r="J67" s="33">
-        <f>J66*Ввод!$D$28</f>
+        <f>J66*incr_3</f>
         <v/>
       </c>
       <c r="K67" s="33">
-        <f>K66*Ввод!$D$28</f>
+        <f>K66*incr_3</f>
         <v/>
       </c>
       <c r="L67" s="33">
-        <f>L66*Ввод!$D$28</f>
+        <f>L66*incr_3</f>
         <v/>
       </c>
       <c r="M67" s="33">
-        <f>M66*Ввод!$D$28</f>
+        <f>M66*incr_3</f>
         <v/>
       </c>
       <c r="N67" s="33">
-        <f>N66*Ввод!$D$28</f>
+        <f>N66*incr_3</f>
         <v/>
       </c>
       <c r="O67" s="33">
-        <f>O66*Ввод!$D$28</f>
+        <f>O66*incr_3</f>
         <v/>
       </c>
       <c r="P67" s="33">
-        <f>P66*Ввод!$D$28</f>
+        <f>P66*incr_3</f>
         <v/>
       </c>
       <c r="Q67" s="33">
-        <f>Q66*Ввод!$D$28</f>
+        <f>Q66*incr_3</f>
         <v/>
       </c>
       <c r="R67" s="33">
-        <f>R66*Ввод!$D$28</f>
+        <f>R66*incr_3</f>
         <v/>
       </c>
       <c r="S67" s="33">
-        <f>S66*Ввод!$D$28</f>
+        <f>S66*incr_3</f>
         <v/>
       </c>
       <c r="T67" s="33">
-        <f>T66*Ввод!$D$28</f>
+        <f>T66*incr_3</f>
         <v/>
       </c>
       <c r="U67" s="33">
-        <f>U66*Ввод!$D$28</f>
+        <f>U66*incr_3</f>
         <v/>
       </c>
       <c r="V67" s="33">
-        <f>V66*Ввод!$D$28</f>
+        <f>V66*incr_3</f>
         <v/>
       </c>
       <c r="W67" s="33">
-        <f>W66*Ввод!$D$28</f>
+        <f>W66*incr_3</f>
         <v/>
       </c>
       <c r="X67" s="33">
-        <f>X66*Ввод!$D$28</f>
+        <f>X66*incr_3</f>
         <v/>
       </c>
       <c r="Y67" s="33">
-        <f>Y66*Ввод!$D$28</f>
+        <f>Y66*incr_3</f>
         <v/>
       </c>
     </row>
@@ -8006,99 +8091,99 @@
         </is>
       </c>
       <c r="B69" s="35">
-        <f>B66/(Ввод!$B$7-B68+B66)</f>
+        <f>B66/(mp_rev-B68+B66)</f>
         <v/>
       </c>
       <c r="C69" s="35">
-        <f>C66/(Ввод!$B$7-C68+C66)</f>
+        <f>C66/(mp_rev-C68+C66)</f>
         <v/>
       </c>
       <c r="D69" s="35">
-        <f>D66/(Ввод!$B$7-D68+D66)</f>
+        <f>D66/(mp_rev-D68+D66)</f>
         <v/>
       </c>
       <c r="E69" s="35">
-        <f>E66/(Ввод!$B$7-E68+E66)</f>
+        <f>E66/(mp_rev-E68+E66)</f>
         <v/>
       </c>
       <c r="F69" s="35">
-        <f>F66/(Ввод!$B$7-F68+F66)</f>
+        <f>F66/(mp_rev-F68+F66)</f>
         <v/>
       </c>
       <c r="G69" s="35">
-        <f>G66/(Ввод!$B$7-G68+G66)</f>
+        <f>G66/(mp_rev-G68+G66)</f>
         <v/>
       </c>
       <c r="H69" s="35">
-        <f>H66/(Ввод!$B$7-H68+H66)</f>
+        <f>H66/(mp_rev-H68+H66)</f>
         <v/>
       </c>
       <c r="I69" s="35">
-        <f>I66/(Ввод!$B$7-I68+I66)</f>
+        <f>I66/(mp_rev-I68+I66)</f>
         <v/>
       </c>
       <c r="J69" s="35">
-        <f>J66/(Ввод!$B$7-J68+J66)</f>
+        <f>J66/(mp_rev-J68+J66)</f>
         <v/>
       </c>
       <c r="K69" s="35">
-        <f>K66/(Ввод!$B$7-K68+K66)</f>
+        <f>K66/(mp_rev-K68+K66)</f>
         <v/>
       </c>
       <c r="L69" s="35">
-        <f>L66/(Ввод!$B$7-L68+L66)</f>
+        <f>L66/(mp_rev-L68+L66)</f>
         <v/>
       </c>
       <c r="M69" s="35">
-        <f>M66/(Ввод!$B$7-M68+M66)</f>
+        <f>M66/(mp_rev-M68+M66)</f>
         <v/>
       </c>
       <c r="N69" s="35">
-        <f>N66/(Ввод!$B$7-N68+N66)</f>
+        <f>N66/(mp_rev-N68+N66)</f>
         <v/>
       </c>
       <c r="O69" s="35">
-        <f>O66/(Ввод!$B$7-O68+O66)</f>
+        <f>O66/(mp_rev-O68+O66)</f>
         <v/>
       </c>
       <c r="P69" s="35">
-        <f>P66/(Ввод!$B$7-P68+P66)</f>
+        <f>P66/(mp_rev-P68+P66)</f>
         <v/>
       </c>
       <c r="Q69" s="35">
-        <f>Q66/(Ввод!$B$7-Q68+Q66)</f>
+        <f>Q66/(mp_rev-Q68+Q66)</f>
         <v/>
       </c>
       <c r="R69" s="35">
-        <f>R66/(Ввод!$B$7-R68+R66)</f>
+        <f>R66/(mp_rev-R68+R66)</f>
         <v/>
       </c>
       <c r="S69" s="35">
-        <f>S66/(Ввод!$B$7-S68+S66)</f>
+        <f>S66/(mp_rev-S68+S66)</f>
         <v/>
       </c>
       <c r="T69" s="35">
-        <f>T66/(Ввод!$B$7-T68+T66)</f>
+        <f>T66/(mp_rev-T68+T66)</f>
         <v/>
       </c>
       <c r="U69" s="35">
-        <f>U66/(Ввод!$B$7-U68+U66)</f>
+        <f>U66/(mp_rev-U68+U66)</f>
         <v/>
       </c>
       <c r="V69" s="35">
-        <f>V66/(Ввод!$B$7-V68+V66)</f>
+        <f>V66/(mp_rev-V68+V66)</f>
         <v/>
       </c>
       <c r="W69" s="35">
-        <f>W66/(Ввод!$B$7-W68+W66)</f>
+        <f>W66/(mp_rev-W68+W66)</f>
         <v/>
       </c>
       <c r="X69" s="35">
-        <f>X66/(Ввод!$B$7-X68+X66)</f>
+        <f>X66/(mp_rev-X68+X66)</f>
         <v/>
       </c>
       <c r="Y69" s="35">
-        <f>Y66/(Ввод!$B$7-Y68+Y66)</f>
+        <f>Y66/(mp_rev-Y68+Y66)</f>
         <v/>
       </c>
     </row>
@@ -8109,99 +8194,99 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>B66*Ввод!$B$32+B64*(Ввод!$B$33+Ввод!$B$34)+B60*B65*Ввод!$B$35+B61*B65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>B66*acq+B64*(ship+pick)+B60*B65*crm_pct+B61*B65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="C70" s="33">
-        <f>C66*Ввод!$B$32+C64*(Ввод!$B$33+Ввод!$B$34)+C60*C65*Ввод!$B$35+C61*C65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>C66*acq+C64*(ship+pick)+C60*C65*crm_pct+C61*C65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="D70" s="33">
-        <f>D66*Ввод!$B$32+D64*(Ввод!$B$33+Ввод!$B$34)+D60*D65*Ввод!$B$35+D61*D65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>D66*acq+D64*(ship+pick)+D60*D65*crm_pct+D61*D65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="E70" s="33">
-        <f>E66*Ввод!$B$32+E64*(Ввод!$B$33+Ввод!$B$34)+E60*E65*Ввод!$B$35+E61*E65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>E66*acq+E64*(ship+pick)+E60*E65*crm_pct+E61*E65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="F70" s="33">
-        <f>F66*Ввод!$B$32+F64*(Ввод!$B$33+Ввод!$B$34)+F60*F65*Ввод!$B$35+F61*F65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>F66*acq+F64*(ship+pick)+F60*F65*crm_pct+F61*F65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="G70" s="33">
-        <f>G66*Ввод!$B$32+G64*(Ввод!$B$33+Ввод!$B$34)+G60*G65*Ввод!$B$35+G61*G65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>G66*acq+G64*(ship+pick)+G60*G65*crm_pct+G61*G65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="H70" s="33">
-        <f>H66*Ввод!$B$32+H64*(Ввод!$B$33+Ввод!$B$34)+H60*H65*Ввод!$B$35+H61*H65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>H66*acq+H64*(ship+pick)+H60*H65*crm_pct+H61*H65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="I70" s="33">
-        <f>I66*Ввод!$B$32+I64*(Ввод!$B$33+Ввод!$B$34)+I60*I65*Ввод!$B$35+I61*I65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>I66*acq+I64*(ship+pick)+I60*I65*crm_pct+I61*I65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="J70" s="33">
-        <f>J66*Ввод!$B$32+J64*(Ввод!$B$33+Ввод!$B$34)+J60*J65*Ввод!$B$35+J61*J65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>J66*acq+J64*(ship+pick)+J60*J65*crm_pct+J61*J65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="K70" s="33">
-        <f>K66*Ввод!$B$32+K64*(Ввод!$B$33+Ввод!$B$34)+K60*K65*Ввод!$B$35+K61*K65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>K66*acq+K64*(ship+pick)+K60*K65*crm_pct+K61*K65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="L70" s="33">
-        <f>L66*Ввод!$B$32+L64*(Ввод!$B$33+Ввод!$B$34)+L60*L65*Ввод!$B$35+L61*L65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>L66*acq+L64*(ship+pick)+L60*L65*crm_pct+L61*L65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="M70" s="33">
-        <f>M66*Ввод!$B$32+M64*(Ввод!$B$33+Ввод!$B$34)+M60*M65*Ввод!$B$35+M61*M65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>M66*acq+M64*(ship+pick)+M60*M65*crm_pct+M61*M65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="N70" s="33">
-        <f>N66*Ввод!$B$32+N64*(Ввод!$B$33+Ввод!$B$34)+N60*N65*Ввод!$B$35+N61*N65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>N66*acq+N64*(ship+pick)+N60*N65*crm_pct+N61*N65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="O70" s="33">
-        <f>O66*Ввод!$B$32+O64*(Ввод!$B$33+Ввод!$B$34)+O60*O65*Ввод!$B$35+O61*O65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>O66*acq+O64*(ship+pick)+O60*O65*crm_pct+O61*O65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="P70" s="33">
-        <f>P66*Ввод!$B$32+P64*(Ввод!$B$33+Ввод!$B$34)+P60*P65*Ввод!$B$35+P61*P65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>P66*acq+P64*(ship+pick)+P60*P65*crm_pct+P61*P65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="Q70" s="33">
-        <f>Q66*Ввод!$B$32+Q64*(Ввод!$B$33+Ввод!$B$34)+Q60*Q65*Ввод!$B$35+Q61*Q65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>Q66*acq+Q64*(ship+pick)+Q60*Q65*crm_pct+Q61*Q65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="R70" s="33">
-        <f>R66*Ввод!$B$32+R64*(Ввод!$B$33+Ввод!$B$34)+R60*R65*Ввод!$B$35+R61*R65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>R66*acq+R64*(ship+pick)+R60*R65*crm_pct+R61*R65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="S70" s="33">
-        <f>S66*Ввод!$B$32+S64*(Ввод!$B$33+Ввод!$B$34)+S60*S65*Ввод!$B$35+S61*S65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>S66*acq+S64*(ship+pick)+S60*S65*crm_pct+S61*S65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="T70" s="33">
-        <f>T66*Ввод!$B$32+T64*(Ввод!$B$33+Ввод!$B$34)+T60*T65*Ввод!$B$35+T61*T65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>T66*acq+T64*(ship+pick)+T60*T65*crm_pct+T61*T65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="U70" s="33">
-        <f>U66*Ввод!$B$32+U64*(Ввод!$B$33+Ввод!$B$34)+U60*U65*Ввод!$B$35+U61*U65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>U66*acq+U64*(ship+pick)+U60*U65*crm_pct+U61*U65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="V70" s="33">
-        <f>V66*Ввод!$B$32+V64*(Ввод!$B$33+Ввод!$B$34)+V60*V65*Ввод!$B$35+V61*V65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>V66*acq+V64*(ship+pick)+V60*V65*crm_pct+V61*V65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="W70" s="33">
-        <f>W66*Ввод!$B$32+W64*(Ввод!$B$33+Ввод!$B$34)+W60*W65*Ввод!$B$35+W61*W65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>W66*acq+W64*(ship+pick)+W60*W65*crm_pct+W61*W65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="X70" s="33">
-        <f>X66*Ввод!$B$32+X64*(Ввод!$B$33+Ввод!$B$34)+X60*X65*Ввод!$B$35+X61*X65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>X66*acq+X64*(ship+pick)+X60*X65*crm_pct+X61*X65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
       <c r="Y70" s="33">
-        <f>Y66*Ввод!$B$32+Y64*(Ввод!$B$33+Ввод!$B$34)+Y60*Y65*Ввод!$B$35+Y61*Y65*Ввод!$B$36+Ввод!$D$24+Ввод!$B$37</f>
+        <f>Y66*acq+Y64*(ship+pick)+Y60*Y65*crm_pct+Y61*Y65*brand_cost+ads_budget_3+platform</f>
         <v/>
       </c>
     </row>
@@ -8315,99 +8400,99 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>Ввод!$B$40+Ввод!$B$41+B66*Ввод!$B$42</f>
+        <f>svc_setup+svc_month+B66*svc_pct</f>
         <v/>
       </c>
       <c r="C72" s="33">
-        <f>Ввод!$B$41+C66*Ввод!$B$42</f>
+        <f>svc_month+C66*svc_pct</f>
         <v/>
       </c>
       <c r="D72" s="33">
-        <f>Ввод!$B$41+D66*Ввод!$B$42</f>
+        <f>svc_month+D66*svc_pct</f>
         <v/>
       </c>
       <c r="E72" s="33">
-        <f>Ввод!$B$41+E66*Ввод!$B$42</f>
+        <f>svc_month+E66*svc_pct</f>
         <v/>
       </c>
       <c r="F72" s="33">
-        <f>Ввод!$B$41+F66*Ввод!$B$42</f>
+        <f>svc_month+F66*svc_pct</f>
         <v/>
       </c>
       <c r="G72" s="33">
-        <f>Ввод!$B$41+G66*Ввод!$B$42</f>
+        <f>svc_month+G66*svc_pct</f>
         <v/>
       </c>
       <c r="H72" s="33">
-        <f>Ввод!$B$41+H66*Ввод!$B$42</f>
+        <f>svc_month+H66*svc_pct</f>
         <v/>
       </c>
       <c r="I72" s="33">
-        <f>Ввод!$B$41+I66*Ввод!$B$42</f>
+        <f>svc_month+I66*svc_pct</f>
         <v/>
       </c>
       <c r="J72" s="33">
-        <f>Ввод!$B$41+J66*Ввод!$B$42</f>
+        <f>svc_month+J66*svc_pct</f>
         <v/>
       </c>
       <c r="K72" s="33">
-        <f>Ввод!$B$41+K66*Ввод!$B$42</f>
+        <f>svc_month+K66*svc_pct</f>
         <v/>
       </c>
       <c r="L72" s="33">
-        <f>Ввод!$B$41+L66*Ввод!$B$42</f>
+        <f>svc_month+L66*svc_pct</f>
         <v/>
       </c>
       <c r="M72" s="33">
-        <f>Ввод!$B$41+M66*Ввод!$B$42</f>
+        <f>svc_month+M66*svc_pct</f>
         <v/>
       </c>
       <c r="N72" s="33">
-        <f>Ввод!$B$41+N66*Ввод!$B$42</f>
+        <f>svc_month+N66*svc_pct</f>
         <v/>
       </c>
       <c r="O72" s="33">
-        <f>Ввод!$B$41+O66*Ввод!$B$42</f>
+        <f>svc_month+O66*svc_pct</f>
         <v/>
       </c>
       <c r="P72" s="33">
-        <f>Ввод!$B$41+P66*Ввод!$B$42</f>
+        <f>svc_month+P66*svc_pct</f>
         <v/>
       </c>
       <c r="Q72" s="33">
-        <f>Ввод!$B$41+Q66*Ввод!$B$42</f>
+        <f>svc_month+Q66*svc_pct</f>
         <v/>
       </c>
       <c r="R72" s="33">
-        <f>Ввод!$B$41+R66*Ввод!$B$42</f>
+        <f>svc_month+R66*svc_pct</f>
         <v/>
       </c>
       <c r="S72" s="33">
-        <f>Ввод!$B$41+S66*Ввод!$B$42</f>
+        <f>svc_month+S66*svc_pct</f>
         <v/>
       </c>
       <c r="T72" s="33">
-        <f>Ввод!$B$41+T66*Ввод!$B$42</f>
+        <f>svc_month+T66*svc_pct</f>
         <v/>
       </c>
       <c r="U72" s="33">
-        <f>Ввод!$B$41+U66*Ввод!$B$42</f>
+        <f>svc_month+U66*svc_pct</f>
         <v/>
       </c>
       <c r="V72" s="33">
-        <f>Ввод!$B$41+V66*Ввод!$B$42</f>
+        <f>svc_month+V66*svc_pct</f>
         <v/>
       </c>
       <c r="W72" s="33">
-        <f>Ввод!$B$41+W66*Ввод!$B$42</f>
+        <f>svc_month+W66*svc_pct</f>
         <v/>
       </c>
       <c r="X72" s="33">
-        <f>Ввод!$B$41+X66*Ввод!$B$42</f>
+        <f>svc_month+X66*svc_pct</f>
         <v/>
       </c>
       <c r="Y72" s="33">
-        <f>Ввод!$B$41+Y66*Ввод!$B$42</f>
+        <f>svc_month+Y66*svc_pct</f>
         <v/>
       </c>
     </row>
@@ -8418,99 +8503,99 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>B66*(1-Ввод!$B$10)-B70-B72</f>
+        <f>B66*(1-cogs)-B70-B72</f>
         <v/>
       </c>
       <c r="C73" s="33">
-        <f>C66*(1-Ввод!$B$10)-C70-C72</f>
+        <f>C66*(1-cogs)-C70-C72</f>
         <v/>
       </c>
       <c r="D73" s="33">
-        <f>D66*(1-Ввод!$B$10)-D70-D72</f>
+        <f>D66*(1-cogs)-D70-D72</f>
         <v/>
       </c>
       <c r="E73" s="33">
-        <f>E66*(1-Ввод!$B$10)-E70-E72</f>
+        <f>E66*(1-cogs)-E70-E72</f>
         <v/>
       </c>
       <c r="F73" s="33">
-        <f>F66*(1-Ввод!$B$10)-F70-F72</f>
+        <f>F66*(1-cogs)-F70-F72</f>
         <v/>
       </c>
       <c r="G73" s="33">
-        <f>G66*(1-Ввод!$B$10)-G70-G72</f>
+        <f>G66*(1-cogs)-G70-G72</f>
         <v/>
       </c>
       <c r="H73" s="33">
-        <f>H66*(1-Ввод!$B$10)-H70-H72</f>
+        <f>H66*(1-cogs)-H70-H72</f>
         <v/>
       </c>
       <c r="I73" s="33">
-        <f>I66*(1-Ввод!$B$10)-I70-I72</f>
+        <f>I66*(1-cogs)-I70-I72</f>
         <v/>
       </c>
       <c r="J73" s="33">
-        <f>J66*(1-Ввод!$B$10)-J70-J72</f>
+        <f>J66*(1-cogs)-J70-J72</f>
         <v/>
       </c>
       <c r="K73" s="33">
-        <f>K66*(1-Ввод!$B$10)-K70-K72</f>
+        <f>K66*(1-cogs)-K70-K72</f>
         <v/>
       </c>
       <c r="L73" s="33">
-        <f>L66*(1-Ввод!$B$10)-L70-L72</f>
+        <f>L66*(1-cogs)-L70-L72</f>
         <v/>
       </c>
       <c r="M73" s="33">
-        <f>M66*(1-Ввод!$B$10)-M70-M72</f>
+        <f>M66*(1-cogs)-M70-M72</f>
         <v/>
       </c>
       <c r="N73" s="33">
-        <f>N66*(1-Ввод!$B$10)-N70-N72</f>
+        <f>N66*(1-cogs)-N70-N72</f>
         <v/>
       </c>
       <c r="O73" s="33">
-        <f>O66*(1-Ввод!$B$10)-O70-O72</f>
+        <f>O66*(1-cogs)-O70-O72</f>
         <v/>
       </c>
       <c r="P73" s="33">
-        <f>P66*(1-Ввод!$B$10)-P70-P72</f>
+        <f>P66*(1-cogs)-P70-P72</f>
         <v/>
       </c>
       <c r="Q73" s="33">
-        <f>Q66*(1-Ввод!$B$10)-Q70-Q72</f>
+        <f>Q66*(1-cogs)-Q70-Q72</f>
         <v/>
       </c>
       <c r="R73" s="33">
-        <f>R66*(1-Ввод!$B$10)-R70-R72</f>
+        <f>R66*(1-cogs)-R70-R72</f>
         <v/>
       </c>
       <c r="S73" s="33">
-        <f>S66*(1-Ввод!$B$10)-S70-S72</f>
+        <f>S66*(1-cogs)-S70-S72</f>
         <v/>
       </c>
       <c r="T73" s="33">
-        <f>T66*(1-Ввод!$B$10)-T70-T72</f>
+        <f>T66*(1-cogs)-T70-T72</f>
         <v/>
       </c>
       <c r="U73" s="33">
-        <f>U66*(1-Ввод!$B$10)-U70-U72</f>
+        <f>U66*(1-cogs)-U70-U72</f>
         <v/>
       </c>
       <c r="V73" s="33">
-        <f>V66*(1-Ввод!$B$10)-V70-V72</f>
+        <f>V66*(1-cogs)-V70-V72</f>
         <v/>
       </c>
       <c r="W73" s="33">
-        <f>W66*(1-Ввод!$B$10)-W70-W72</f>
+        <f>W66*(1-cogs)-W70-W72</f>
         <v/>
       </c>
       <c r="X73" s="33">
-        <f>X66*(1-Ввод!$B$10)-X70-X72</f>
+        <f>X66*(1-cogs)-X70-X72</f>
         <v/>
       </c>
       <c r="Y73" s="33">
-        <f>Y66*(1-Ввод!$B$10)-Y70-Y72</f>
+        <f>Y66*(1-cogs)-Y70-Y72</f>
         <v/>
       </c>
     </row>
@@ -8521,99 +8606,99 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>B68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>B68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="C74" s="33">
-        <f>C68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>C68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="D74" s="33">
-        <f>D68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>D68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="E74" s="33">
-        <f>E68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>E68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="F74" s="33">
-        <f>F68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>F68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="G74" s="33">
-        <f>G68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>G68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="H74" s="33">
-        <f>H68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>H68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="I74" s="33">
-        <f>I68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>I68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="J74" s="33">
-        <f>J68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>J68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="K74" s="33">
-        <f>K68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>K68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="L74" s="33">
-        <f>L68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>L68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="M74" s="33">
-        <f>M68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>M68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="N74" s="33">
-        <f>N68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>N68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="O74" s="33">
-        <f>O68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>O68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="P74" s="33">
-        <f>P68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>P68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Q74" s="33">
-        <f>Q68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Q68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="R74" s="33">
-        <f>R68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>R68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="S74" s="33">
-        <f>S68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>S68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="T74" s="33">
-        <f>T68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>T68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="U74" s="33">
-        <f>U68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>U68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="V74" s="33">
-        <f>V68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>V68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="W74" s="33">
-        <f>W68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>W68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="X74" s="33">
-        <f>X68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>X68*(1-cogs-mp_take)</f>
         <v/>
       </c>
       <c r="Y74" s="33">
-        <f>Y68*(1-Ввод!$B$10-Ввод!$B$9)</f>
+        <f>Y68*(1-cogs-mp_take)</f>
         <v/>
       </c>
     </row>
@@ -8937,7 +9022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9380,6 +9465,116 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>«Телодвижения»: выручка</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2021: 102 млн → 2024: 4,7 млрд → 2025: &gt;7 млрд ₽</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Business Vector; Forbes 30 до 30, 05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>«Телодвижения»: свой сайт</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>запущен только в 03.2026, доля не раскрыта</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Sostav, блог бренда 11.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Bungly (детская одежда)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>маркетплейсы 56% продаж, свой сайт + франшиза</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>shoppers.media</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Штраф WB за «бонус за отзыв» во вкладыше</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>50 000 ₽ за факт</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Перечень штрафов WB с 01.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Адрес своего сайта в чате WB</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>разрешён (Telegram и соцсети — нет, штраф 25 000 ₽)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Перечень штрафов WB, п. 8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
